--- a/Results/Phase 2/Hydrogen/hydrogen resource use mineral and metals results.xlsx
+++ b/Results/Phase 2/Hydrogen/hydrogen resource use mineral and metals results.xlsx
@@ -886,7 +886,7 @@
         <v>7.014900893156962e-06</v>
       </c>
       <c r="N5" t="n">
-        <v>0.000187562788357144</v>
+        <v>7.014900893156959e-06</v>
       </c>
       <c r="O5" t="n">
         <v>7.014900893156959e-06</v>
@@ -974,7 +974,7 @@
         <v>3.382557843099994e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>0.000187562788357144</v>
+        <v>1.498973547156052e-05</v>
       </c>
       <c r="O6" t="n">
         <v>1.498973691819228e-05</v>
@@ -1062,7 +1062,7 @@
         <v>5.872263734785052e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>0.000187562788357144</v>
+        <v>5.872263734785052e-05</v>
       </c>
       <c r="O7" t="n">
         <v>5.87224781726672e-05</v>
@@ -1150,7 +1150,7 @@
         <v>0.00042782896081624</v>
       </c>
       <c r="N8" t="n">
-        <v>0.000187562788357144</v>
+        <v>0.0003005382315500037</v>
       </c>
       <c r="O8" t="n">
         <v>0.0003355188292149006</v>
@@ -1238,7 +1238,7 @@
         <v>0.0002181029543485374</v>
       </c>
       <c r="N9" t="n">
-        <v>0.000187562788357144</v>
+        <v>0.0002181029543485374</v>
       </c>
       <c r="O9" t="n">
         <v>0.0002333899318469625</v>
@@ -1922,7 +1922,7 @@
         <v>7.427427332855529e-06</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0001863512412236642</v>
+        <v>7.427427332855531e-06</v>
       </c>
       <c r="O5" t="n">
         <v>7.427427332855531e-06</v>
@@ -2010,7 +2010,7 @@
         <v>1.455086438747029e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0001863512412236642</v>
+        <v>1.456686954825057e-05</v>
       </c>
       <c r="O6" t="n">
         <v>3.1504505547649e-05</v>
@@ -2098,7 +2098,7 @@
         <v>5.273131867383941e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0001863512412236642</v>
+        <v>5.273131867383941e-05</v>
       </c>
       <c r="O7" t="n">
         <v>5.273113673597674e-05</v>
@@ -2186,7 +2186,7 @@
         <v>0.0003753994046666724</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0001863512412236642</v>
+        <v>0.0002640501946150037</v>
       </c>
       <c r="O8" t="n">
         <v>0.0002946499243794354</v>
@@ -2274,7 +2274,7 @@
         <v>0.000162583928639447</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0001863512412236642</v>
+        <v>0.000162583928639447</v>
       </c>
       <c r="O9" t="n">
         <v>0.0001738488783679051</v>
@@ -2958,7 +2958,7 @@
         <v>7.033242474236019e-06</v>
       </c>
       <c r="N5" t="n">
-        <v>0.000184637907155414</v>
+        <v>7.033242474236e-06</v>
       </c>
       <c r="O5" t="n">
         <v>7.033242474236e-06</v>
@@ -3046,7 +3046,7 @@
         <v>3.221957330069292e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>0.000184637907155414</v>
+        <v>1.452116359942012e-05</v>
       </c>
       <c r="O6" t="n">
         <v>1.451995741582333e-05</v>
@@ -3134,7 +3134,7 @@
         <v>5.542712165399521e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>0.000184637907155414</v>
+        <v>5.542712165399521e-05</v>
       </c>
       <c r="O7" t="n">
         <v>5.542695110092184e-05</v>
@@ -3222,7 +3222,7 @@
         <v>0.00040093555743774</v>
       </c>
       <c r="N8" t="n">
-        <v>0.000184637907155414</v>
+        <v>0.0002817817950080431</v>
       </c>
       <c r="O8" t="n">
         <v>0.0003145262835331086</v>
@@ -3310,7 +3310,7 @@
         <v>0.0001910766000856583</v>
       </c>
       <c r="N9" t="n">
-        <v>0.000184637907155414</v>
+        <v>0.0001910766000856583</v>
       </c>
       <c r="O9" t="n">
         <v>0.0002044143010656408</v>
@@ -3694,85 +3694,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.461668545005744e-05</v>
+        <v>2.461668545005739e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>2.457942010891398e-05</v>
+        <v>2.457942010891394e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>2.465970245480251e-05</v>
+        <v>2.46597024548025e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>2.290005485436979e-05</v>
+        <v>2.290005485436975e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>2.457222565645199e-05</v>
+        <v>2.457222565645194e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>2.464873420833619e-05</v>
+        <v>2.464873420833613e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>2.459225633397754e-05</v>
+        <v>2.459225633397753e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>2.464160597704234e-05</v>
+        <v>2.464160597704226e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>2.458548847751171e-05</v>
+        <v>2.458548847751147e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>2.465694518331461e-05</v>
+        <v>2.465694518331459e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>2.460429631842116e-05</v>
+        <v>2.460429631842113e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>2.463563729536098e-05</v>
+        <v>2.463563729536095e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>2.460532089286509e-05</v>
+        <v>2.460532089286505e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>2.45753973230037e-05</v>
+        <v>2.457539732300365e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>2.457659061131365e-05</v>
+        <v>2.457659061131359e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.459919903242955e-05</v>
+        <v>2.459919903242953e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>2.4605672447016e-05</v>
+        <v>2.460567244701598e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>2.46195667811251e-05</v>
+        <v>2.461956678112513e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>2.462250113574389e-05</v>
+        <v>2.462250113574386e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>2.461099854538161e-05</v>
+        <v>2.461099854538166e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>2.516829679193875e-05</v>
+        <v>2.516829679193885e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>2.468654332697617e-05</v>
+        <v>2.468654332697613e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>2.46115278222215e-05</v>
+        <v>2.461152782222152e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.459776241157377e-05</v>
+        <v>2.459776241157374e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.462774806127228e-05</v>
+        <v>2.462774806127226e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.46292850661922e-05</v>
+        <v>2.462928506619215e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.465058723917521e-05</v>
+        <v>2.465058723917518e-05</v>
       </c>
     </row>
     <row r="3">
@@ -3782,85 +3782,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.440887051211618e-05</v>
+        <v>2.440887051211611e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>2.440887051211618e-05</v>
+        <v>2.440887051211611e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>2.440887051211618e-05</v>
+        <v>2.440887051211611e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>2.278747009205413e-05</v>
+        <v>2.278747009205411e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>2.440887051211618e-05</v>
+        <v>2.440887051211611e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>2.440887051211618e-05</v>
+        <v>2.440887051211611e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>2.440887051211618e-05</v>
+        <v>2.440887051211611e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>2.440887051211618e-05</v>
+        <v>2.440887051211611e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>2.436875594199447e-05</v>
+        <v>2.436875594199441e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>2.440887051211618e-05</v>
+        <v>2.440887051211611e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>2.440887051211618e-05</v>
+        <v>2.440887051211611e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>2.440887051211618e-05</v>
+        <v>2.440887051211611e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>2.440887051211618e-05</v>
+        <v>2.440887051211611e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>2.440887051211618e-05</v>
+        <v>2.440887051211611e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>2.440887051211618e-05</v>
+        <v>2.440887051211611e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.440887051211618e-05</v>
+        <v>2.440887051211611e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>2.440887051211618e-05</v>
+        <v>2.440887051211611e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>2.440887051211618e-05</v>
+        <v>2.440887051211611e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>2.440887051211618e-05</v>
+        <v>2.440887051211611e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>2.440887051211618e-05</v>
+        <v>2.440887051211611e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>2.498013315054424e-05</v>
+        <v>2.498013315054423e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>2.440887051211618e-05</v>
+        <v>2.440887051211611e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>2.440887051211618e-05</v>
+        <v>2.440887051211611e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.440887051211618e-05</v>
+        <v>2.440887051211611e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.440887051211618e-05</v>
+        <v>2.440887051211611e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.440887051211618e-05</v>
+        <v>2.440887051211611e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.440887051211618e-05</v>
+        <v>2.440887051211611e-05</v>
       </c>
     </row>
     <row r="4">
@@ -3870,85 +3870,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0001772437871274898</v>
+        <v>0.00017724378712749</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0001973987685308584</v>
+        <v>0.0001973987685308581</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0001959974051469249</v>
+        <v>0.0001959974051469264</v>
       </c>
       <c r="E4" t="n">
-        <v>5.125304921170055e-05</v>
+        <v>5.125304921170048e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0001834623283580667</v>
+        <v>0.0001834623283580665</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0001921066277553694</v>
+        <v>0.0001921066277553702</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0001815353258302114</v>
+        <v>0.0001815353258302077</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0001904141345039543</v>
+        <v>0.0001904141345039539</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0001877715641536743</v>
+        <v>0.000187771564153676</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0002348063026577842</v>
+        <v>0.0002348063026577845</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0001733131661232492</v>
+        <v>0.0001733131661232487</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0001949906771975275</v>
+        <v>0.0001949906771975266</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0001756181141486109</v>
+        <v>0.0001756181141486115</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0001849784713573645</v>
+        <v>0.0001849784713573641</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0001664627045670845</v>
+        <v>0.0001664627045670807</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0001820382372327113</v>
+        <v>0.0001820382372327105</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0001805794179886754</v>
+        <v>0.0001805794179886757</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0001833915915988239</v>
+        <v>0.000183391591598824</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0001840255410460997</v>
+        <v>0.0001840255410461014</v>
       </c>
       <c r="U4" t="n">
-        <v>0.000183315059264121</v>
+        <v>0.0001833150592641491</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0002035786082480263</v>
+        <v>0.0002035786082480303</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0001938716729276663</v>
+        <v>0.0001938716729276658</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0001834504402418469</v>
+        <v>0.0001834504402418466</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0001798316954744234</v>
+        <v>0.0001798316954744238</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.00019486935501156</v>
+        <v>0.0001948693550115602</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0001815549819726036</v>
+        <v>0.000181554981972603</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0002016616944105736</v>
+        <v>0.0002016616944105735</v>
       </c>
     </row>
     <row r="5">
@@ -3958,85 +3958,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.165540626371411e-06</v>
+        <v>7.165540626371371e-06</v>
       </c>
       <c r="C5" t="n">
-        <v>7.165540626371416e-06</v>
+        <v>7.165540626371349e-06</v>
       </c>
       <c r="D5" t="n">
-        <v>7.165540626371416e-06</v>
+        <v>7.165540626371349e-06</v>
       </c>
       <c r="E5" t="n">
-        <v>7.165540626371416e-06</v>
+        <v>7.165540626371349e-06</v>
       </c>
       <c r="F5" t="n">
-        <v>7.16554062637141e-06</v>
+        <v>7.165540626371367e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>7.165540626371416e-06</v>
+        <v>7.165540626371349e-06</v>
       </c>
       <c r="H5" t="n">
-        <v>7.165540626371416e-06</v>
+        <v>7.165540626371349e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>7.165540626371416e-06</v>
+        <v>7.165540626371349e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>7.100254439825354e-06</v>
+        <v>7.100254439825323e-06</v>
       </c>
       <c r="K5" t="n">
-        <v>7.165540626371416e-06</v>
+        <v>7.165540626371349e-06</v>
       </c>
       <c r="L5" t="n">
-        <v>7.165540626371414e-06</v>
+        <v>7.165540626371349e-06</v>
       </c>
       <c r="M5" t="n">
-        <v>7.165540626371416e-06</v>
+        <v>7.165540626371349e-06</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0001756181141486109</v>
+        <v>7.165540626371367e-06</v>
       </c>
       <c r="O5" t="n">
-        <v>7.16554062637141e-06</v>
+        <v>7.165540626371367e-06</v>
       </c>
       <c r="P5" t="n">
-        <v>7.16554062637141e-06</v>
+        <v>7.165540626371367e-06</v>
       </c>
       <c r="Q5" t="n">
-        <v>7.16554062637141e-06</v>
+        <v>7.165540626371367e-06</v>
       </c>
       <c r="R5" t="n">
-        <v>7.165540626371416e-06</v>
+        <v>7.165540626371349e-06</v>
       </c>
       <c r="S5" t="n">
-        <v>7.165540626371416e-06</v>
+        <v>7.165540626371349e-06</v>
       </c>
       <c r="T5" t="n">
-        <v>7.165540626371416e-06</v>
+        <v>7.165540626371349e-06</v>
       </c>
       <c r="U5" t="n">
-        <v>6.78653428784416e-06</v>
+        <v>6.78653428784415e-06</v>
       </c>
       <c r="V5" t="n">
-        <v>6.892283028608153e-06</v>
+        <v>6.892283028608077e-06</v>
       </c>
       <c r="W5" t="n">
-        <v>7.16554062637141e-06</v>
+        <v>7.165540626371367e-06</v>
       </c>
       <c r="X5" t="n">
-        <v>7.165540626371411e-06</v>
+        <v>7.165540626371371e-06</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.78653428784416e-06</v>
+        <v>6.78653428784415e-06</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.165540626371416e-06</v>
+        <v>7.165540626371349e-06</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.165540626371416e-06</v>
+        <v>7.165540626371349e-06</v>
       </c>
       <c r="AB5" t="n">
-        <v>7.16554062637141e-06</v>
+        <v>7.165540626371367e-06</v>
       </c>
     </row>
     <row r="6">
@@ -4046,85 +4046,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.081719853930717e-05</v>
+        <v>3.081719853930727e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.415923133306845e-05</v>
+        <v>1.415923133306844e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>3.08171985393072e-05</v>
+        <v>3.081719853930727e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>3.08171985393072e-05</v>
+        <v>3.081719853930727e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.415923133306845e-05</v>
+        <v>1.415923133306844e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.415923133306845e-05</v>
+        <v>1.415923133306844e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.415923133306845e-05</v>
+        <v>1.415923133306844e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.415923133306845e-05</v>
+        <v>1.415923133306844e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>3.075191235276103e-05</v>
+        <v>3.075191235276128e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>3.08171985393072e-05</v>
+        <v>3.081719853930727e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>3.081719853930717e-05</v>
+        <v>3.081719853930727e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>1.415923133306845e-05</v>
+        <v>1.415923133306844e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0001756181141486109</v>
+        <v>1.416994229139989e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>3.087310215262704e-05</v>
+        <v>3.087310215262691e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>3.087359221249012e-05</v>
+        <v>3.087359221249007e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.08171985393072e-05</v>
+        <v>3.081719853930727e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>1.415923133306845e-05</v>
+        <v>1.415923133306844e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>3.08171985393072e-05</v>
+        <v>3.081719853930727e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.415923133306845e-05</v>
+        <v>1.415923133306844e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>1.415923133306845e-05</v>
+        <v>1.415923133306844e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>3.054394094154393e-05</v>
+        <v>3.054394094154396e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>3.087249813367204e-05</v>
+        <v>3.087249813367208e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>1.415923133306845e-05</v>
+        <v>1.415923133306844e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.454291991629547e-05</v>
+        <v>1.45429199162954e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.08171985393072e-05</v>
+        <v>3.081719853930727e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.08171985393072e-05</v>
+        <v>3.081719853930727e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.417158042909442e-05</v>
+        <v>1.417158042909439e-05</v>
       </c>
     </row>
     <row r="7">
@@ -4134,85 +4134,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.232846938451507e-05</v>
+        <v>5.232846938451503e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>5.232846938451502e-05</v>
+        <v>5.232846938451503e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>5.232846938451502e-05</v>
+        <v>5.232846938451503e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>5.232846938451502e-05</v>
+        <v>5.232846938451503e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>5.232846938451502e-05</v>
+        <v>5.232846938451503e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>5.232846938451502e-05</v>
+        <v>5.232846938451503e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>5.232846938451502e-05</v>
+        <v>5.232846938451503e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>5.232846938451502e-05</v>
+        <v>5.232846938451503e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>5.226318319796907e-05</v>
+        <v>5.226318319796896e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>5.232846938451502e-05</v>
+        <v>5.232846938451503e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>5.232846938451507e-05</v>
+        <v>5.232846938451503e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>5.232846938451502e-05</v>
+        <v>5.232846938451503e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0001756181141486109</v>
+        <v>5.232846938451503e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>5.232829528489885e-05</v>
+        <v>5.232829528489886e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>5.232829528489885e-05</v>
+        <v>5.232829528489886e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.232846938451502e-05</v>
+        <v>5.232846938451503e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>5.232846938451502e-05</v>
+        <v>5.232846938451503e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>5.232846938451502e-05</v>
+        <v>5.232846938451503e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>5.232846938451502e-05</v>
+        <v>5.232846938451503e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>5.233065754132706e-05</v>
+        <v>5.233065754132694e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>5.205521178675178e-05</v>
+        <v>5.205521178675171e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>5.232846938451502e-05</v>
+        <v>5.232846938451503e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>5.232846938451507e-05</v>
+        <v>5.232846938451503e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.232846938451502e-05</v>
+        <v>5.232846938451503e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.232846938451502e-05</v>
+        <v>5.232846938451503e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.232846938451502e-05</v>
+        <v>5.232846938451503e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.232846938451502e-05</v>
+        <v>5.232846938451503e-05</v>
       </c>
     </row>
     <row r="8">
@@ -4222,73 +4222,73 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0002311961244407155</v>
+        <v>0.0002311961244407154</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0003746036567713666</v>
+        <v>0.0003746036567713669</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0003746036567713666</v>
+        <v>0.0003746036567713669</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0002982433760577406</v>
+        <v>0.0002982433760577405</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0002535373419416747</v>
+        <v>0.0002535373419416746</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0004043401428151557</v>
+        <v>0.0004043401428151555</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0003746036567713666</v>
+        <v>0.0003746036567713669</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0003746036567713666</v>
+        <v>0.0003746036567713669</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0003745383705848207</v>
+        <v>0.0003745383705848206</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0003746036567713666</v>
+        <v>0.0003746036567713669</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0003746036567713669</v>
+        <v>0.0003746036567713671</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0003746036567713629</v>
+        <v>0.0003746036567713626</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0001756181141486109</v>
+        <v>0.0002634388276642375</v>
       </c>
       <c r="O8" t="n">
         <v>0.0002939878879443994</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0002864995750994927</v>
+        <v>0.0002864995750994922</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0002030132712138299</v>
+        <v>0.00020301327121383</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0003746036567713666</v>
+        <v>0.0003746036567713669</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0003746036567713666</v>
+        <v>0.0003746036567713669</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0003746036567713666</v>
+        <v>0.0003746036567713669</v>
       </c>
       <c r="U8" t="n">
-        <v>0.000304610184985778</v>
+        <v>0.0003046101849857779</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0003351369774772422</v>
+        <v>0.000335136977477242</v>
       </c>
       <c r="W8" t="n">
-        <v>0.000374631840486322</v>
+        <v>0.0003746318404863216</v>
       </c>
       <c r="X8" t="n">
-        <v>0.000216156856522783</v>
+        <v>0.0002161568565227834</v>
       </c>
       <c r="Y8" t="n">
         <v>0.0005171936337874018</v>
@@ -4297,10 +4297,10 @@
         <v>0.0002285322559000418</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.0003746036567713666</v>
+        <v>0.0003746036567713669</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0005244048158573264</v>
+        <v>0.0005244048158573265</v>
       </c>
     </row>
     <row r="9">
@@ -4310,85 +4310,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0001337002584035246</v>
+        <v>0.0001337002584035244</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0001691559189817227</v>
+        <v>0.0001691559189817224</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0001691559189817227</v>
+        <v>0.0001691559189817224</v>
       </c>
       <c r="E9" t="n">
         <v>0.0001609728981407481</v>
       </c>
       <c r="F9" t="n">
-        <v>8.742094288511035e-05</v>
+        <v>8.742094288511012e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0001691559202810783</v>
+        <v>0.000169155920281078</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0001691559189817227</v>
+        <v>0.0001691559189817224</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0001691559189817227</v>
+        <v>0.0001691559189817224</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0001690906327951764</v>
+        <v>0.0001690906327951763</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0001691559189817227</v>
+        <v>0.0001691559189817224</v>
       </c>
       <c r="L9" t="n">
         <v>0.0001691559189817225</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0001691559189817227</v>
+        <v>0.0001691559189817224</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0001756181141486109</v>
+        <v>0.0001691559189817224</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0001809058802020618</v>
+        <v>0.0001809058802020614</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0001834612948895197</v>
+        <v>0.0001834612948895198</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0001691559202810783</v>
+        <v>0.000169155920281078</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0001691559189817227</v>
+        <v>0.0001691559189817224</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0001691559189817227</v>
+        <v>0.0001691559189817224</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0001691559189817227</v>
+        <v>0.0001691559189817224</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0001691559189817227</v>
+        <v>0.0001691559189817224</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0002097977339916903</v>
+        <v>0.0002097977339916904</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0001691559189817227</v>
+        <v>0.0001691559189817224</v>
       </c>
       <c r="X9" t="n">
         <v>0.0001691559189817225</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.0001691559189817227</v>
+        <v>0.0001691559189817224</v>
       </c>
       <c r="Z9" t="n">
         <v>0.0001477793090093801</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.0001691559189817227</v>
+        <v>0.0001691559189817224</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.0001691559189817227</v>
+        <v>0.0001691559189817224</v>
       </c>
     </row>
     <row r="10">
@@ -4398,85 +4398,85 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.373625808611308e-05</v>
+        <v>2.373625808611303e-05</v>
       </c>
       <c r="C10" t="n">
-        <v>2.396804281427157e-05</v>
+        <v>2.396804281427153e-05</v>
       </c>
       <c r="D10" t="n">
-        <v>2.349856918109627e-05</v>
+        <v>2.349856918109625e-05</v>
       </c>
       <c r="E10" t="n">
-        <v>2.221209546764736e-05</v>
+        <v>2.221209546764737e-05</v>
       </c>
       <c r="F10" t="n">
         <v>2.40141826448232e-05</v>
       </c>
       <c r="G10" t="n">
-        <v>2.354623413764774e-05</v>
+        <v>2.354623413764761e-05</v>
       </c>
       <c r="H10" t="n">
-        <v>2.389892387090325e-05</v>
+        <v>2.389892387090319e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>2.360655187739658e-05</v>
+        <v>2.360655187739653e-05</v>
       </c>
       <c r="J10" t="n">
-        <v>2.363789765828276e-05</v>
+        <v>2.36378976582828e-05</v>
       </c>
       <c r="K10" t="n">
-        <v>2.351310811022232e-05</v>
+        <v>2.351310811022228e-05</v>
       </c>
       <c r="L10" t="n">
-        <v>2.381531594975884e-05</v>
+        <v>2.381531594975881e-05</v>
       </c>
       <c r="M10" t="n">
-        <v>2.364341532409731e-05</v>
+        <v>2.364341532409728e-05</v>
       </c>
       <c r="N10" t="n">
-        <v>2.381354314672824e-05</v>
+        <v>2.381354314672821e-05</v>
       </c>
       <c r="O10" t="n">
-        <v>2.398113214140351e-05</v>
+        <v>2.398113214140349e-05</v>
       </c>
       <c r="P10" t="n">
-        <v>2.397342894009377e-05</v>
+        <v>2.397342894009374e-05</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.385088519039867e-05</v>
+        <v>2.38508851903986e-05</v>
       </c>
       <c r="R10" t="n">
-        <v>2.381840406911463e-05</v>
+        <v>2.381840406911458e-05</v>
       </c>
       <c r="S10" t="n">
-        <v>2.372203195931293e-05</v>
+        <v>2.372203195931289e-05</v>
       </c>
       <c r="T10" t="n">
-        <v>2.371708567032433e-05</v>
+        <v>2.371708567032435e-05</v>
       </c>
       <c r="U10" t="n">
-        <v>2.377481320091337e-05</v>
+        <v>2.377481320091302e-05</v>
       </c>
       <c r="V10" t="n">
-        <v>2.435960135813827e-05</v>
+        <v>2.435960135813837e-05</v>
       </c>
       <c r="W10" t="n">
-        <v>2.333129718983009e-05</v>
+        <v>2.333129718983005e-05</v>
       </c>
       <c r="X10" t="n">
-        <v>2.377987692773608e-05</v>
+        <v>2.377987692773607e-05</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.385658550616666e-05</v>
+        <v>2.385658550616662e-05</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.367155844982159e-05</v>
+        <v>2.367155844982156e-05</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.367008095497547e-05</v>
+        <v>2.367008095497545e-05</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.355208055296445e-05</v>
+        <v>2.355208055296444e-05</v>
       </c>
     </row>
     <row r="11">
@@ -4486,85 +4486,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.431064465273739e-05</v>
+        <v>2.431064465273738e-05</v>
       </c>
       <c r="C11" t="n">
-        <v>2.437884210156017e-05</v>
+        <v>2.437884210156016e-05</v>
       </c>
       <c r="D11" t="n">
-        <v>2.424551244823026e-05</v>
+        <v>2.424551244823021e-05</v>
       </c>
       <c r="E11" t="n">
         <v>2.263825756665458e-05</v>
       </c>
       <c r="F11" t="n">
-        <v>2.439264141903807e-05</v>
+        <v>2.439264141903804e-05</v>
       </c>
       <c r="G11" t="n">
-        <v>2.425623190889402e-05</v>
+        <v>2.425623190889395e-05</v>
       </c>
       <c r="H11" t="n">
-        <v>2.436022898712219e-05</v>
+        <v>2.436022898712212e-05</v>
       </c>
       <c r="I11" t="n">
-        <v>2.427654844140708e-05</v>
+        <v>2.427654844140711e-05</v>
       </c>
       <c r="J11" t="n">
-        <v>2.425294562931574e-05</v>
+        <v>2.425294562931565e-05</v>
       </c>
       <c r="K11" t="n">
-        <v>2.424937043582753e-05</v>
+        <v>2.424937043582754e-05</v>
       </c>
       <c r="L11" t="n">
-        <v>2.433422710100244e-05</v>
+        <v>2.43342271010024e-05</v>
       </c>
       <c r="M11" t="n">
         <v>2.428735274545145e-05</v>
       </c>
       <c r="N11" t="n">
-        <v>2.433444504441783e-05</v>
+        <v>2.433444504441778e-05</v>
       </c>
       <c r="O11" t="n">
-        <v>2.438077500120816e-05</v>
+        <v>2.438077500120814e-05</v>
       </c>
       <c r="P11" t="n">
-        <v>2.437846330837355e-05</v>
+        <v>2.437846330837347e-05</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.434531393285439e-05</v>
+        <v>2.434531393285434e-05</v>
       </c>
       <c r="R11" t="n">
-        <v>2.433700833374542e-05</v>
+        <v>2.43370083337454e-05</v>
       </c>
       <c r="S11" t="n">
-        <v>2.430705305077509e-05</v>
+        <v>2.430705305077504e-05</v>
       </c>
       <c r="T11" t="n">
-        <v>2.430773682814119e-05</v>
+        <v>2.43077368281411e-05</v>
       </c>
       <c r="U11" t="n">
-        <v>2.432250044816362e-05</v>
+        <v>2.432250044816366e-05</v>
       </c>
       <c r="V11" t="n">
-        <v>2.488595284887655e-05</v>
+        <v>2.488595284887666e-05</v>
       </c>
       <c r="W11" t="n">
-        <v>2.419624403131356e-05</v>
+        <v>2.419624403131354e-05</v>
       </c>
       <c r="X11" t="n">
-        <v>2.432533373684496e-05</v>
+        <v>2.432533373684498e-05</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.434647097383888e-05</v>
+        <v>2.434647097383884e-05</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.429226872325414e-05</v>
+        <v>2.429226872325412e-05</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.42931334633105e-05</v>
+        <v>2.429313346331052e-05</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.426074507733361e-05</v>
+        <v>2.426074507733357e-05</v>
       </c>
     </row>
   </sheetData>
@@ -4730,85 +4730,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.468790056087224e-05</v>
+        <v>2.468790056087222e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>2.464772807820109e-05</v>
+        <v>2.464772807820106e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>2.477839391963972e-05</v>
+        <v>2.47783939196397e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>2.293931639944582e-05</v>
+        <v>2.293931639944583e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>2.464669418437253e-05</v>
+        <v>2.464669418437247e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>2.47325045504534e-05</v>
+        <v>2.473250455045338e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>2.468171465307897e-05</v>
+        <v>2.468171465307899e-05</v>
       </c>
       <c r="I2" t="n">
         <v>2.473228231574996e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>2.466545191321505e-05</v>
+        <v>2.466545191321501e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>2.471505981005076e-05</v>
+        <v>2.471505981005071e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>2.466827982627337e-05</v>
+        <v>2.466827982627332e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>2.471547918174594e-05</v>
+        <v>2.471547918174591e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>2.466945850758203e-05</v>
+        <v>2.466945850758204e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>2.466489387230479e-05</v>
+        <v>2.466489387230477e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>2.465434294399498e-05</v>
+        <v>2.465434294399497e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.466227357498771e-05</v>
+        <v>2.466227357498773e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>2.467782069791096e-05</v>
+        <v>2.467782069791092e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>2.468268325277299e-05</v>
+        <v>2.4682683252773e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>2.47097216929952e-05</v>
+        <v>2.470972169299517e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>2.468450966537205e-05</v>
+        <v>2.468450966537207e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>2.526715409533352e-05</v>
+        <v>2.526715409533355e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>2.479512301495316e-05</v>
+        <v>2.47951230149531e-05</v>
       </c>
       <c r="X2" t="n">
         <v>2.467855962752932e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.468296766601538e-05</v>
+        <v>2.46829676660153e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.470332055886235e-05</v>
+        <v>2.470332055886236e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.473026596717639e-05</v>
+        <v>2.473026596717638e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.473669098301703e-05</v>
+        <v>2.473669098301702e-05</v>
       </c>
     </row>
     <row r="3">
@@ -4818,85 +4818,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.447611742314736e-05</v>
+        <v>2.447611742314735e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>2.447611742314736e-05</v>
+        <v>2.447611742314735e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>2.447611742314736e-05</v>
+        <v>2.447611742314735e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>2.28184295505566e-05</v>
+        <v>2.281842955055659e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>2.447611742314736e-05</v>
+        <v>2.447611742314735e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>2.447611742314736e-05</v>
+        <v>2.447611742314735e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>2.447611742314736e-05</v>
+        <v>2.447611742314735e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>2.447611742314736e-05</v>
+        <v>2.447611742314735e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>2.443612432295343e-05</v>
+        <v>2.44361243229534e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>2.447611742314736e-05</v>
+        <v>2.447611742314735e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>2.447611742314736e-05</v>
+        <v>2.447611742314735e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>2.447611742314736e-05</v>
+        <v>2.447611742314735e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>2.447611742314736e-05</v>
+        <v>2.447611742314735e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>2.447611742314736e-05</v>
+        <v>2.447611742314735e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>2.447611742314736e-05</v>
+        <v>2.447611742314735e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.447611742314736e-05</v>
+        <v>2.447611742314735e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>2.447611742314736e-05</v>
+        <v>2.447611742314735e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>2.447611742314736e-05</v>
+        <v>2.447611742314735e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>2.447611742314736e-05</v>
+        <v>2.447611742314735e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>2.447611742314736e-05</v>
+        <v>2.447611742314735e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>2.506057255943692e-05</v>
+        <v>2.506057255943693e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>2.447611742314736e-05</v>
+        <v>2.447611742314735e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>2.447611742314736e-05</v>
+        <v>2.447611742314735e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.447611742314736e-05</v>
+        <v>2.447611742314735e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.447611742314736e-05</v>
+        <v>2.447611742314735e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.447611742314736e-05</v>
+        <v>2.447611742314735e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.447611742314736e-05</v>
+        <v>2.447611742314735e-05</v>
       </c>
     </row>
     <row r="4">
@@ -4906,85 +4906,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0001877590284274388</v>
+        <v>0.0001877590284274387</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0002004419777509588</v>
+        <v>0.0002004419777509581</v>
       </c>
       <c r="D4" t="n">
-        <v>0.000225357893301457</v>
+        <v>0.0002253578933014617</v>
       </c>
       <c r="E4" t="n">
-        <v>7.537484803325374e-05</v>
+        <v>7.537484803325356e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>0.000187361884318925</v>
+        <v>0.0001873618843189221</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0002090144692445091</v>
+        <v>0.0002090144692445065</v>
       </c>
       <c r="H4" t="n">
         <v>0.0001864730226391208</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0002041034237564223</v>
+        <v>0.0002041034237564218</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0002002825702596365</v>
+        <v>0.0002002825702596338</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0002316772003922256</v>
+        <v>0.0002316772003922243</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0001883323675244777</v>
+        <v>0.0001883323675244767</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0002150718344495604</v>
+        <v>0.0002150718344495574</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0001743834282481711</v>
+        <v>0.000174383428248171</v>
       </c>
       <c r="O4" t="n">
         <v>0.000189049261836262</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0001810681437145058</v>
+        <v>0.0001810681437145042</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.000186747886571515</v>
+        <v>0.0001867478865715147</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0001821432058939786</v>
+        <v>0.0001821432058939776</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0001859814319190595</v>
+        <v>0.0001859814319190627</v>
       </c>
       <c r="T4" t="n">
-        <v>0.000189022770116119</v>
+        <v>0.0001890227701161198</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0001983753288217761</v>
+        <v>0.0001983753288217748</v>
       </c>
       <c r="V4" t="n">
-        <v>0.000210895524292084</v>
+        <v>0.0002108955242920828</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0002039370146585621</v>
+        <v>0.0002039370146585594</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0001918111909049885</v>
+        <v>0.000191811190904986</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0001764838774007134</v>
+        <v>0.0001764838774007053</v>
       </c>
       <c r="Z4" t="n">
         <v>0.0002096525719557135</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.000188056540361573</v>
+        <v>0.0001880565403615717</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.000210096428544182</v>
+        <v>0.0002100964285441812</v>
       </c>
     </row>
     <row r="5">
@@ -4994,85 +4994,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.284104908163016e-06</v>
+        <v>7.284104908163069e-06</v>
       </c>
       <c r="C5" t="n">
-        <v>7.284104908162994e-06</v>
+        <v>7.284104908163089e-06</v>
       </c>
       <c r="D5" t="n">
-        <v>7.284104908162994e-06</v>
+        <v>7.284104908163089e-06</v>
       </c>
       <c r="E5" t="n">
-        <v>7.284104908162994e-06</v>
+        <v>7.284104908163089e-06</v>
       </c>
       <c r="F5" t="n">
-        <v>7.284104908163015e-06</v>
+        <v>7.28410490816305e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>7.284104908162994e-06</v>
+        <v>7.284104908163089e-06</v>
       </c>
       <c r="H5" t="n">
-        <v>7.284104908162994e-06</v>
+        <v>7.284104908163089e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>7.284104908162994e-06</v>
+        <v>7.284104908163089e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>7.218866597020273e-06</v>
+        <v>7.218866597020343e-06</v>
       </c>
       <c r="K5" t="n">
-        <v>7.284104908162994e-06</v>
+        <v>7.284104908163089e-06</v>
       </c>
       <c r="L5" t="n">
-        <v>7.284104908163003e-06</v>
+        <v>7.28410490816309e-06</v>
       </c>
       <c r="M5" t="n">
-        <v>7.284104908162994e-06</v>
+        <v>7.284104908163089e-06</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0001743834282481711</v>
+        <v>7.28410490816305e-06</v>
       </c>
       <c r="O5" t="n">
-        <v>7.284104908163015e-06</v>
+        <v>7.28410490816305e-06</v>
       </c>
       <c r="P5" t="n">
-        <v>7.284104908163015e-06</v>
+        <v>7.28410490816305e-06</v>
       </c>
       <c r="Q5" t="n">
-        <v>7.284104908163015e-06</v>
+        <v>7.28410490816305e-06</v>
       </c>
       <c r="R5" t="n">
-        <v>7.284104908162994e-06</v>
+        <v>7.284104908163089e-06</v>
       </c>
       <c r="S5" t="n">
-        <v>7.284104908162994e-06</v>
+        <v>7.284104908163089e-06</v>
       </c>
       <c r="T5" t="n">
-        <v>7.284104908162994e-06</v>
+        <v>7.284104908163089e-06</v>
       </c>
       <c r="U5" t="n">
-        <v>6.919262077176758e-06</v>
+        <v>6.919262077176775e-06</v>
       </c>
       <c r="V5" t="n">
-        <v>7.011193420731154e-06</v>
+        <v>7.011193420731178e-06</v>
       </c>
       <c r="W5" t="n">
-        <v>7.284104908163015e-06</v>
+        <v>7.28410490816305e-06</v>
       </c>
       <c r="X5" t="n">
-        <v>7.284104908163022e-06</v>
+        <v>7.284104908163058e-06</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.919262077176758e-06</v>
+        <v>6.919262077176775e-06</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.284104908162994e-06</v>
+        <v>7.284104908163089e-06</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.284104908162994e-06</v>
+        <v>7.284104908163089e-06</v>
       </c>
       <c r="AB5" t="n">
-        <v>7.284104908163015e-06</v>
+        <v>7.28410490816305e-06</v>
       </c>
     </row>
     <row r="6">
@@ -5082,85 +5082,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.430534846857702e-05</v>
+        <v>1.430534846857701e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.430534846857702e-05</v>
+        <v>1.430534846857701e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>3.103264191181385e-05</v>
+        <v>3.103264191181376e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>3.103264191181385e-05</v>
+        <v>3.103264191181376e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.430534846857702e-05</v>
+        <v>1.430534846857701e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.430534846857702e-05</v>
+        <v>1.430534846857701e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>3.103264191181385e-05</v>
+        <v>3.103264191181376e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.430534846857702e-05</v>
+        <v>1.430534846857701e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>3.096740360067106e-05</v>
+        <v>3.096740360067091e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>3.103264191181385e-05</v>
+        <v>3.103264191181376e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.430534846857702e-05</v>
+        <v>1.430534846857701e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>1.430534846857702e-05</v>
+        <v>1.430534846857701e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0001743834282481711</v>
+        <v>1.431610131239659e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>1.431500866071905e-05</v>
+        <v>1.431500866071915e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>3.108842255019939e-05</v>
+        <v>3.10884225501997e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.103264191181385e-05</v>
+        <v>3.103264191181376e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>3.103264191181385e-05</v>
+        <v>3.103264191181376e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>1.430534846857702e-05</v>
+        <v>1.430534846857701e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>3.103264191181385e-05</v>
+        <v>3.103264191181376e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>3.103264191181385e-05</v>
+        <v>3.103264191181376e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>1.403243698114526e-05</v>
+        <v>1.403243698114511e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>1.476432963001582e-05</v>
+        <v>1.476432963001576e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>1.430534846857702e-05</v>
+        <v>1.430534846857701e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.469192431999882e-05</v>
+        <v>1.469192431999887e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.430534846857702e-05</v>
+        <v>1.430534846857701e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.103264191181385e-05</v>
+        <v>3.103264191181376e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.431827593782322e-05</v>
+        <v>1.431827593782331e-05</v>
       </c>
     </row>
     <row r="7">
@@ -5170,85 +5170,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.248589402639916e-05</v>
+        <v>5.2485894026399e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>5.248589402639913e-05</v>
+        <v>5.2485894026399e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>5.248589402639913e-05</v>
+        <v>5.2485894026399e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>5.248589402639913e-05</v>
+        <v>5.2485894026399e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>5.248589402639913e-05</v>
+        <v>5.2485894026399e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>5.248589402639913e-05</v>
+        <v>5.2485894026399e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>5.248589402639913e-05</v>
+        <v>5.2485894026399e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>5.248589402639913e-05</v>
+        <v>5.2485894026399e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>5.242065571525632e-05</v>
+        <v>5.242065571525635e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>5.248589402639913e-05</v>
+        <v>5.2485894026399e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>5.248589402639917e-05</v>
+        <v>5.2485894026399e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>5.248589402639913e-05</v>
+        <v>5.2485894026399e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0001743834282481711</v>
+        <v>5.2485894026399e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>5.24857146919675e-05</v>
+        <v>5.248571469196737e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>5.24857146919675e-05</v>
+        <v>5.248571469196737e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.248589402639913e-05</v>
+        <v>5.2485894026399e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>5.248589402639913e-05</v>
+        <v>5.2485894026399e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>5.248589402639913e-05</v>
+        <v>5.2485894026399e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>5.248589402639913e-05</v>
+        <v>5.2485894026399e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>5.249261304920526e-05</v>
+        <v>5.249261304920503e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>5.221298253896728e-05</v>
+        <v>5.221298253896715e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>5.248589402639913e-05</v>
+        <v>5.2485894026399e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>5.248589402639917e-05</v>
+        <v>5.2485894026399e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.248589402639913e-05</v>
+        <v>5.2485894026399e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.248589402639913e-05</v>
+        <v>5.2485894026399e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.248589402639913e-05</v>
+        <v>5.2485894026399e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.248589402639913e-05</v>
+        <v>5.2485894026399e-05</v>
       </c>
     </row>
     <row r="8">
@@ -5258,85 +5258,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0002314141695197247</v>
+        <v>0.0002314141695197238</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0003749026952809305</v>
+        <v>0.0003749026952809297</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0003749026952809305</v>
+        <v>0.0003749026952809297</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0002984992879547107</v>
+        <v>0.0002984992879547099</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0002537680048505386</v>
+        <v>0.0002537680048505378</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0004046559758401607</v>
+        <v>0.0004046559758401596</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0003749026952809305</v>
+        <v>0.0003749026952809297</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0003749026952809305</v>
+        <v>0.0003749026952809297</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0003748374569697875</v>
+        <v>0.0003748374569697871</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0003749026952809305</v>
+        <v>0.0003749026952809297</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0003749026952809306</v>
+        <v>0.0003749026952809295</v>
       </c>
       <c r="M8" t="n">
-        <v>0.000374902695280928</v>
+        <v>0.0003749026952809272</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0001743834282481711</v>
+        <v>0.0002636750827151569</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0002942413964348147</v>
+        <v>0.0002942413964348139</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0002867488543549941</v>
+        <v>0.0002867488543549934</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0002032153992351678</v>
+        <v>0.0002032153992351675</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0003749026952809305</v>
+        <v>0.0003749026952809297</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0003749026952809305</v>
+        <v>0.0003749026952809297</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0003749026952809305</v>
+        <v>0.0003749026952809297</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0003048732070495658</v>
+        <v>0.0003048732070495653</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0003354181027179069</v>
+        <v>0.0003354181027179064</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0003749308949132475</v>
+        <v>0.0003749308949132467</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0002163664077528738</v>
+        <v>0.0002163664077528733</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0005175792159911888</v>
+        <v>0.0005175792159911879</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.0002287487964844891</v>
+        <v>0.0002287487964844886</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.0003749026952809305</v>
+        <v>0.0003749026952809297</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0005247884587775465</v>
+        <v>0.000524788458777545</v>
       </c>
     </row>
     <row r="9">
@@ -5346,7 +5346,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0001278480201692861</v>
+        <v>0.0001278480201692859</v>
       </c>
       <c r="C9" t="n">
         <v>0.0001616601656535275</v>
@@ -5355,13 +5355,13 @@
         <v>0.0001616601656535275</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0001538564614734634</v>
+        <v>0.0001538564614734628</v>
       </c>
       <c r="F9" t="n">
-        <v>8.371394026886047e-05</v>
+        <v>8.371394026886032e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0001616601670581877</v>
+        <v>0.0001616601670581872</v>
       </c>
       <c r="H9" t="n">
         <v>0.0001616601656535275</v>
@@ -5370,28 +5370,28 @@
         <v>0.0001616601656535275</v>
       </c>
       <c r="J9" t="n">
-        <v>0.000161594927342385</v>
+        <v>0.0001615949273423846</v>
       </c>
       <c r="K9" t="n">
         <v>0.0001616601656535275</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0001616601656535275</v>
+        <v>0.0001616601656535276</v>
       </c>
       <c r="M9" t="n">
         <v>0.0001616601656535275</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0001743834282481711</v>
+        <v>0.0001616601656535275</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0001728654682639316</v>
+        <v>0.0001728654682639312</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0001753024290255941</v>
+        <v>0.0001753024290255939</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0001616601670581877</v>
+        <v>0.0001616601670581872</v>
       </c>
       <c r="R9" t="n">
         <v>0.0001616601656535275</v>
@@ -5406,19 +5406,19 @@
         <v>0.0001616601656535275</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0002004057453309837</v>
+        <v>0.0002004057453309829</v>
       </c>
       <c r="W9" t="n">
         <v>0.0001616601656535275</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0001616601656535275</v>
+        <v>0.0001616601656535276</v>
       </c>
       <c r="Y9" t="n">
         <v>0.0001616601656535275</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.0001412744491775921</v>
+        <v>0.0001412744491775917</v>
       </c>
       <c r="AA9" t="n">
         <v>0.0001616601656535275</v>
@@ -5434,22 +5434,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.37770825415728e-05</v>
+        <v>2.377708254157285e-05</v>
       </c>
       <c r="C10" t="n">
-        <v>2.402629291721069e-05</v>
+        <v>2.402629291721066e-05</v>
       </c>
       <c r="D10" t="n">
-        <v>2.326170682201965e-05</v>
+        <v>2.326170682201971e-05</v>
       </c>
       <c r="E10" t="n">
-        <v>2.21944895013369e-05</v>
+        <v>2.219448950133691e-05</v>
       </c>
       <c r="F10" t="n">
-        <v>2.403657760312814e-05</v>
+        <v>2.403657760312816e-05</v>
       </c>
       <c r="G10" t="n">
-        <v>2.351242157229399e-05</v>
+        <v>2.351242157229414e-05</v>
       </c>
       <c r="H10" t="n">
         <v>2.383419182184747e-05</v>
@@ -5458,61 +5458,61 @@
         <v>2.353405113833834e-05</v>
       </c>
       <c r="J10" t="n">
-        <v>2.363088909082363e-05</v>
+        <v>2.363088909082373e-05</v>
       </c>
       <c r="K10" t="n">
-        <v>2.363114836293115e-05</v>
+        <v>2.363114836293117e-05</v>
       </c>
       <c r="L10" t="n">
-        <v>2.389905845969721e-05</v>
+        <v>2.389905845969722e-05</v>
       </c>
       <c r="M10" t="n">
-        <v>2.363440618441201e-05</v>
+        <v>2.363440618441209e-05</v>
       </c>
       <c r="N10" t="n">
-        <v>2.389629690067699e-05</v>
+        <v>2.3896296900677e-05</v>
       </c>
       <c r="O10" t="n">
         <v>2.391304992055895e-05</v>
       </c>
       <c r="P10" t="n">
-        <v>2.397523307146961e-05</v>
+        <v>2.397523307146963e-05</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.393985604259585e-05</v>
+        <v>2.393985604259582e-05</v>
       </c>
       <c r="R10" t="n">
-        <v>2.385429420088103e-05</v>
+        <v>2.385429420088102e-05</v>
       </c>
       <c r="S10" t="n">
-        <v>2.381096952920745e-05</v>
+        <v>2.381096952920746e-05</v>
       </c>
       <c r="T10" t="n">
-        <v>2.366464120354456e-05</v>
+        <v>2.366464120354453e-05</v>
       </c>
       <c r="U10" t="n">
-        <v>2.380219021167528e-05</v>
+        <v>2.380219021167522e-05</v>
       </c>
       <c r="V10" t="n">
-        <v>2.432664501532426e-05</v>
+        <v>2.432664501532439e-05</v>
       </c>
       <c r="W10" t="n">
-        <v>2.315180667516264e-05</v>
+        <v>2.315180667516265e-05</v>
       </c>
       <c r="X10" t="n">
         <v>2.384561116917274e-05</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.381522602407674e-05</v>
+        <v>2.381522602407677e-05</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.36865180719749e-05</v>
+        <v>2.368651807197487e-05</v>
       </c>
       <c r="AA10" t="n">
         <v>2.353560239278529e-05</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.350612766789585e-05</v>
+        <v>2.350612766789587e-05</v>
       </c>
     </row>
     <row r="11">
@@ -5522,85 +5522,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.436983746206383e-05</v>
+        <v>2.436983746206382e-05</v>
       </c>
       <c r="C11" t="n">
-        <v>2.444305649449425e-05</v>
+        <v>2.444305649449423e-05</v>
       </c>
       <c r="D11" t="n">
-        <v>2.422583322602966e-05</v>
+        <v>2.422583322602967e-05</v>
       </c>
       <c r="E11" t="n">
-        <v>2.265542168867192e-05</v>
+        <v>2.26554216886719e-05</v>
       </c>
       <c r="F11" t="n">
-        <v>2.444670216553348e-05</v>
+        <v>2.444670216553347e-05</v>
       </c>
       <c r="G11" t="n">
-        <v>2.429401986719866e-05</v>
+        <v>2.429401986719869e-05</v>
       </c>
       <c r="H11" t="n">
-        <v>2.4389636458792e-05</v>
+        <v>2.438963645879201e-05</v>
       </c>
       <c r="I11" t="n">
-        <v>2.430363915397476e-05</v>
+        <v>2.430363915397474e-05</v>
       </c>
       <c r="J11" t="n">
-        <v>2.429906731646358e-05</v>
+        <v>2.429906731646359e-05</v>
       </c>
       <c r="K11" t="n">
-        <v>2.433059619489576e-05</v>
+        <v>2.433059619489573e-05</v>
       </c>
       <c r="L11" t="n">
-        <v>2.440571615892576e-05</v>
+        <v>2.440571615892572e-05</v>
       </c>
       <c r="M11" t="n">
-        <v>2.433249788574677e-05</v>
+        <v>2.433249788574678e-05</v>
       </c>
       <c r="N11" t="n">
-        <v>2.440563832207962e-05</v>
+        <v>2.440563832207964e-05</v>
       </c>
       <c r="O11" t="n">
-        <v>2.440869636423741e-05</v>
+        <v>2.440869636423739e-05</v>
       </c>
       <c r="P11" t="n">
         <v>2.442643896775789e-05</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.441827293787318e-05</v>
+        <v>2.441827293787319e-05</v>
       </c>
       <c r="R11" t="n">
-        <v>2.439488915014674e-05</v>
+        <v>2.439488915014673e-05</v>
       </c>
       <c r="S11" t="n">
-        <v>2.438003884132978e-05</v>
+        <v>2.438003884132983e-05</v>
       </c>
       <c r="T11" t="n">
-        <v>2.434049742705467e-05</v>
+        <v>2.434049742705465e-05</v>
       </c>
       <c r="U11" t="n">
         <v>2.437787063647368e-05</v>
       </c>
       <c r="V11" t="n">
-        <v>2.493321472387394e-05</v>
+        <v>2.493321472387401e-05</v>
       </c>
       <c r="W11" t="n">
-        <v>2.419255740429214e-05</v>
+        <v>2.419255740429209e-05</v>
       </c>
       <c r="X11" t="n">
-        <v>2.439167727266667e-05</v>
+        <v>2.439167727266671e-05</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.438225997330231e-05</v>
+        <v>2.43822599733023e-05</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.434405033777507e-05</v>
+        <v>2.434405033777506e-05</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.43023286311181e-05</v>
+        <v>2.430232863111806e-05</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.429534255320372e-05</v>
+        <v>2.429534255320366e-05</v>
       </c>
     </row>
   </sheetData>
@@ -6066,7 +6066,7 @@
         <v>7.132497361873138e-06</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0001955260791175433</v>
+        <v>7.132497361873121e-06</v>
       </c>
       <c r="O5" t="n">
         <v>7.132497361873121e-06</v>
@@ -6154,7 +6154,7 @@
         <v>3.244795572425032e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0001955260791175433</v>
+        <v>1.466840784789715e-05</v>
       </c>
       <c r="O6" t="n">
         <v>3.25125367265473e-05</v>
@@ -6242,7 +6242,7 @@
         <v>5.556982460834477e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0001955260791175433</v>
+        <v>5.556982460834477e-05</v>
       </c>
       <c r="O7" t="n">
         <v>5.556964553532804e-05</v>
@@ -6330,7 +6330,7 @@
         <v>0.0004011968447599428</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0001955260791175433</v>
+        <v>0.0002819848457215194</v>
       </c>
       <c r="O8" t="n">
         <v>0.0003147453381721497</v>
@@ -6418,7 +6418,7 @@
         <v>0.0001915371578482646</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0001955260791175433</v>
+        <v>0.0001915371578482646</v>
       </c>
       <c r="O9" t="n">
         <v>0.0002049030485405351</v>
@@ -6862,7 +6862,7 @@
         <v>2.481619000537518e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>2.539536045778009e-05</v>
+        <v>2.53953604577801e-05</v>
       </c>
       <c r="W2" t="n">
         <v>2.489154325919092e-05</v>
@@ -7102,7 +7102,7 @@
         <v>7.347619124766933e-06</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0001962578656036419</v>
+        <v>7.347619124766877e-06</v>
       </c>
       <c r="O5" t="n">
         <v>7.347619124766875e-06</v>
@@ -7190,7 +7190,7 @@
         <v>3.125714102998714e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0001962578656036419</v>
+        <v>1.445253932484816e-05</v>
       </c>
       <c r="O6" t="n">
         <v>3.131513682757925e-05</v>
@@ -7278,7 +7278,7 @@
         <v>5.260933339755297e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0001962578656036419</v>
+        <v>5.260933339755297e-05</v>
       </c>
       <c r="O7" t="n">
         <v>5.260915296502517e-05</v>
@@ -7330,7 +7330,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0002315652207019407</v>
+        <v>0.0002315652207019408</v>
       </c>
       <c r="C8" t="n">
         <v>0.0003751285484879773</v>
@@ -7366,7 +7366,7 @@
         <v>0.0003751285484879761</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0001962578656036419</v>
+        <v>0.00026384295183878</v>
       </c>
       <c r="O8" t="n">
         <v>0.0002944252000878321</v>
@@ -7454,7 +7454,7 @@
         <v>0.000170031525048171</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0001962578656036419</v>
+        <v>0.000170031525048171</v>
       </c>
       <c r="O9" t="n">
         <v>0.0001818354550594155</v>
@@ -8050,7 +8050,7 @@
         <v>0.0002759153357096588</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0001985928699513997</v>
+        <v>0.0001985928699513996</v>
       </c>
       <c r="O4" t="n">
         <v>0.0002007493244986581</v>
@@ -8138,7 +8138,7 @@
         <v>7.50608862832492e-06</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0001985928699513996</v>
+        <v>7.506088628324934e-06</v>
       </c>
       <c r="O5" t="n">
         <v>7.506088628324934e-06</v>
@@ -8226,7 +8226,7 @@
         <v>3.169708668686243e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0001985928699513997</v>
+        <v>1.469163121316559e-05</v>
       </c>
       <c r="O6" t="n">
         <v>1.469035265563613e-05</v>
@@ -8314,7 +8314,7 @@
         <v>5.287887656217373e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0001985928699513997</v>
+        <v>5.287887656217373e-05</v>
       </c>
       <c r="O7" t="n">
         <v>5.287869237928433e-05</v>
@@ -8402,7 +8402,7 @@
         <v>0.0003757207889944145</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0001985928699513997</v>
+        <v>0.0002642849049390126</v>
       </c>
       <c r="O8" t="n">
         <v>0.0002949084534720679</v>
@@ -8490,7 +8490,7 @@
         <v>0.0001632077841410827</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0001985928699513997</v>
+        <v>0.0001632077841410827</v>
       </c>
       <c r="O9" t="n">
         <v>0.0001745151119122408</v>
@@ -9086,7 +9086,7 @@
         <v>0.0002368680192056151</v>
       </c>
       <c r="N4" t="n">
-        <v>0.000182301564769895</v>
+        <v>0.0001823015647698951</v>
       </c>
       <c r="O4" t="n">
         <v>0.0001991040280961772</v>
@@ -9174,7 +9174,7 @@
         <v>7.054502509477718e-06</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0001823015647698951</v>
+        <v>7.054502509477725e-06</v>
       </c>
       <c r="O5" t="n">
         <v>7.054502509477725e-06</v>
@@ -9262,7 +9262,7 @@
         <v>1.453389917856052e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>0.000182301564769895</v>
+        <v>1.454704299985886e-05</v>
       </c>
       <c r="O6" t="n">
         <v>3.232547534061311e-05</v>
@@ -9350,7 +9350,7 @@
         <v>5.544595054936069e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>0.000182301564769895</v>
+        <v>5.544595054936069e-05</v>
       </c>
       <c r="O7" t="n">
         <v>5.544577793301587e-05</v>
@@ -9438,7 +9438,7 @@
         <v>0.0004009627458213956</v>
       </c>
       <c r="N8" t="n">
-        <v>0.000182301564769895</v>
+        <v>0.0002818054127261403</v>
       </c>
       <c r="O8" t="n">
         <v>0.0003145508825010529</v>
@@ -9526,7 +9526,7 @@
         <v>0.000191115201723876</v>
       </c>
       <c r="N9" t="n">
-        <v>0.000182301564769895</v>
+        <v>0.000191115201723876</v>
       </c>
       <c r="O9" t="n">
         <v>0.0002044545733455404</v>
@@ -10210,7 +10210,7 @@
         <v>7.246293453486447e-06</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0001818234508085234</v>
+        <v>7.246293453486439e-06</v>
       </c>
       <c r="O5" t="n">
         <v>7.246293453486439e-06</v>
@@ -10298,7 +10298,7 @@
         <v>1.429389277435112e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0001818234508085234</v>
+        <v>1.430651037084668e-05</v>
       </c>
       <c r="O6" t="n">
         <v>3.104268171517073e-05</v>
@@ -10386,7 +10386,7 @@
         <v>5.244262880688193e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0001818234508085234</v>
+        <v>5.244262880688193e-05</v>
       </c>
       <c r="O7" t="n">
         <v>5.244245210715234e-05</v>
@@ -10474,7 +10474,7 @@
         <v>0.0003747996785914486</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0001818234508085234</v>
+        <v>0.0002635946142873692</v>
       </c>
       <c r="O8" t="n">
         <v>0.000294154731548893</v>
@@ -10562,7 +10562,7 @@
         <v>0.0001693971649057573</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0001818234508085234</v>
+        <v>0.0001693971649057573</v>
       </c>
       <c r="O9" t="n">
         <v>0.000181159964363435</v>

--- a/Results/Phase 2/Hydrogen/hydrogen resource use mineral and metals results.xlsx
+++ b/Results/Phase 2/Hydrogen/hydrogen resource use mineral and metals results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.44154681532368e-05</v>
+        <v>2.441546815323665e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>2.43791842681422e-05</v>
+        <v>2.437918426814211e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>2.438878742901512e-05</v>
+        <v>2.438878742901511e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>2.276686948694141e-05</v>
+        <v>2.276686948694127e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>2.438584514391093e-05</v>
+        <v>2.438584514391088e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>2.446113304110875e-05</v>
+        <v>2.446113304110864e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>2.440223407935404e-05</v>
+        <v>2.440223407935426e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>2.439792751514792e-05</v>
+        <v>2.43979275151479e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>2.439335162960989e-05</v>
+        <v>2.439335162960978e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>2.441825957784558e-05</v>
+        <v>2.441825957784545e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>2.440359369885517e-05</v>
+        <v>2.440359369885506e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>2.444218446385364e-05</v>
+        <v>2.444218446385358e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>2.440493825275679e-05</v>
+        <v>2.440493825275668e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>2.442774577670718e-05</v>
+        <v>2.442774577670707e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>2.441686373335244e-05</v>
+        <v>2.441686373335237e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.439781295066023e-05</v>
+        <v>2.439781295066011e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>2.438501606751425e-05</v>
+        <v>2.438501606751413e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>2.442115960716972e-05</v>
+        <v>2.442115960716965e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>2.439596699673676e-05</v>
+        <v>2.439596699673661e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>2.444346545922368e-05</v>
+        <v>2.444346545922361e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>2.498385794188506e-05</v>
+        <v>2.498385794188502e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>2.447020691176836e-05</v>
+        <v>2.447020691176825e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>2.441390182736286e-05</v>
+        <v>2.441390182736261e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.444113760985503e-05</v>
+        <v>2.44411376098549e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.442542074343707e-05</v>
+        <v>2.442542074343692e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.441687257811837e-05</v>
+        <v>2.441687257811826e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.445781908090852e-05</v>
+        <v>2.445781908090843e-05</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.425157288862098e-05</v>
+        <v>2.42515728886208e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>2.425157288862098e-05</v>
+        <v>2.42515728886208e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>2.425157288862098e-05</v>
+        <v>2.42515728886208e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>2.269884217892887e-05</v>
+        <v>2.269884217892876e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>2.425157288862098e-05</v>
+        <v>2.42515728886208e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>2.425157288862098e-05</v>
+        <v>2.42515728886208e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>2.425157288862098e-05</v>
+        <v>2.42515728886208e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>2.425157288862098e-05</v>
+        <v>2.42515728886208e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>2.421253068623997e-05</v>
+        <v>2.421253068623983e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>2.425157288862098e-05</v>
+        <v>2.42515728886208e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>2.425157288862098e-05</v>
+        <v>2.42515728886208e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>2.425157288862098e-05</v>
+        <v>2.42515728886208e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>2.425157288862098e-05</v>
+        <v>2.42515728886208e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>2.425157288862098e-05</v>
+        <v>2.42515728886208e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>2.425157288862098e-05</v>
+        <v>2.42515728886208e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.425157288862098e-05</v>
+        <v>2.42515728886208e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>2.425157288862098e-05</v>
+        <v>2.42515728886208e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>2.425157288862098e-05</v>
+        <v>2.42515728886208e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>2.425157288862098e-05</v>
+        <v>2.42515728886208e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>2.425157288862098e-05</v>
+        <v>2.42515728886208e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>2.481326043322076e-05</v>
+        <v>2.481326043322078e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>2.425157288862098e-05</v>
+        <v>2.42515728886208e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>2.425157288862098e-05</v>
+        <v>2.42515728886208e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.425157288862098e-05</v>
+        <v>2.42515728886208e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.425157288862098e-05</v>
+        <v>2.42515728886208e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.425157288862098e-05</v>
+        <v>2.42515728886208e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.425157288862098e-05</v>
+        <v>2.42515728886208e-05</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0001940369666930536</v>
+        <v>0.0001940369666930532</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0001846052567079913</v>
+        <v>0.0001846052567079911</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0001841239759914761</v>
+        <v>0.000184123975991477</v>
       </c>
       <c r="E4" t="n">
-        <v>4.466717740905284e-05</v>
+        <v>4.466717740905314e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0001895469276765953</v>
+        <v>0.0001895469276765949</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0001985402703340714</v>
+        <v>0.0001985402703340696</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0001976195350049849</v>
+        <v>0.0001976195350049848</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0001882526458452453</v>
+        <v>0.0001882526458452449</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0001931815207945166</v>
+        <v>0.0001931815207945165</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0001922174101407974</v>
+        <v>0.000192217410140797</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0001822732707682466</v>
+        <v>0.0001822732707682431</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0002094543394432529</v>
+        <v>0.0002094543394432523</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0001875627883571461</v>
+        <v>0.000187562788357146</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0002061887159033774</v>
+        <v>0.0002061887159033776</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0001824958375672674</v>
+        <v>0.0001824958375672678</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0001870433822840747</v>
+        <v>0.0001870433822840743</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0001857947898382786</v>
+        <v>0.0001857947898382775</v>
       </c>
       <c r="S4" t="n">
-        <v>0.000191994670993661</v>
+        <v>0.0001919946709936611</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0001867649627493189</v>
+        <v>0.0001867649627493226</v>
       </c>
       <c r="U4" t="n">
-        <v>0.000199546070979582</v>
+        <v>0.0001995460709795829</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0002048650898181224</v>
+        <v>0.0002048650898181225</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0002038574584208957</v>
+        <v>0.0002038574584208963</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0001936921132981453</v>
+        <v>0.0001936921132981467</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0002012625518065943</v>
+        <v>0.0002012625518065946</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0001888785408595476</v>
+        <v>0.0001888785408595477</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0001878455880626258</v>
+        <v>0.0001878455880626261</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0002196658323372443</v>
+        <v>0.0002196658323372441</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0002636183060679187</v>
+        <v>0.000263618306067919</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0004278289608162402</v>
+        <v>0.00042782896081624</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0004278289608162402</v>
+        <v>0.00042782896081624</v>
       </c>
       <c r="E5" t="n">
-        <v>0.000340391631068153</v>
+        <v>0.0003403916310681535</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0002892004069109077</v>
+        <v>0.0002892004069109078</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0004618791098133318</v>
+        <v>0.000461879109813332</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0004278289608162402</v>
+        <v>0.00042782896081624</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0004278289608162402</v>
+        <v>0.00042782896081624</v>
       </c>
       <c r="J5" t="n">
-        <v>0.000427763811881209</v>
+        <v>0.0004277638118812092</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0004278289608162402</v>
+        <v>0.00042782896081624</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0004278289608162402</v>
+        <v>0.00042782896081624</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0004278289608162399</v>
+        <v>0.0004278289608162398</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0001875627883571461</v>
+        <v>0.0003005382315500034</v>
       </c>
       <c r="O5" t="n">
         <v>0.0003355188292149007</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0003269442394758003</v>
+        <v>0.0003269442394758014</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0002313471644768941</v>
+        <v>0.0002313471644768936</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0004278289608162402</v>
+        <v>0.00042782896081624</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0004278289608162402</v>
+        <v>0.00042782896081624</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0004278289608162402</v>
+        <v>0.00042782896081624</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0003476794307424873</v>
+        <v>0.0003476794307424875</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0003826747440924291</v>
+        <v>0.0003826747440924293</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0004278612329450442</v>
+        <v>0.0004278612329450448</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0002463973972943887</v>
+        <v>0.000246397397294389</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0005910990197499569</v>
+        <v>0.0005910990197499574</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0002605680088477635</v>
+        <v>0.000260568008847764</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0004278289608162402</v>
+        <v>0.00042782896081624</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0005993607207999675</v>
+        <v>0.0005993607207999678</v>
       </c>
     </row>
     <row r="6">
@@ -941,82 +941,82 @@
         <v>0.0001719742992613295</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0002181029543485377</v>
+        <v>0.0002181029543485375</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0002181029543485377</v>
+        <v>0.0002181029543485375</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0002074566498358024</v>
+        <v>0.0002074566498358016</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0001117638130967002</v>
+        <v>0.0001117638130966999</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0002181029555524277</v>
+        <v>0.0002181029555524273</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0002181029543485377</v>
+        <v>0.0002181029543485375</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0002181029543485377</v>
+        <v>0.0002181029543485375</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0002180378054135065</v>
+        <v>0.000218037805413506</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0002181029543485377</v>
+        <v>0.0002181029543485375</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0002181029543485377</v>
+        <v>0.0002181029543485375</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0002181029543485377</v>
+        <v>0.0002181029543485375</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0001875627883571461</v>
+        <v>0.0002181029543485375</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0002333899318469626</v>
+        <v>0.0002333899318469619</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0002367145869106888</v>
+        <v>0.0002367145869106882</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0002181029555524277</v>
+        <v>0.0002181029555524273</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0002181029543485377</v>
+        <v>0.0002181029543485375</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0002181029543485377</v>
+        <v>0.0002181029543485375</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0002181029543485377</v>
+        <v>0.0002181029543485375</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0002181029543485377</v>
+        <v>0.0002181029543485375</v>
       </c>
       <c r="V6" t="n">
-        <v>0.000271062019136484</v>
+        <v>0.0002710620191364841</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0002181029543485377</v>
+        <v>0.0002181029543485375</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0002181029543485377</v>
+        <v>0.0002181029543485375</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0002181029543485377</v>
+        <v>0.0002181029543485375</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0001902914777290549</v>
+        <v>0.0001902914777290545</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0002181029543485377</v>
+        <v>0.0002181029543485375</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0002181029543485377</v>
+        <v>0.0002181029543485375</v>
       </c>
     </row>
     <row r="7">
@@ -1029,82 +1029,82 @@
         <v>2.384802806324411e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>2.407021849307815e-05</v>
+        <v>2.407021849307817e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.401444975218878e-05</v>
+        <v>2.40144497521886e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.238838427931643e-05</v>
+        <v>2.238838427931632e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.403403056114393e-05</v>
+        <v>2.403403056114374e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.357689480322832e-05</v>
+        <v>2.357689480322816e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.393962758928156e-05</v>
+        <v>2.393962758928118e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.396193177089117e-05</v>
+        <v>2.396193177089088e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.36971089476549e-05</v>
+        <v>2.369710894765467e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>2.384089069983395e-05</v>
+        <v>2.384089069983374e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>2.392235416543225e-05</v>
+        <v>2.392235416543213e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>2.370472557037335e-05</v>
+        <v>2.370472557037314e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>2.391737851466744e-05</v>
+        <v>2.391737851466725e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>2.377417626553208e-05</v>
+        <v>2.377417626553197e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>2.383840937300569e-05</v>
+        <v>2.38384093730054e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.39601779307615e-05</v>
+        <v>2.396017793076129e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>2.403840017997572e-05</v>
+        <v>2.40384001799756e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>2.381630465303348e-05</v>
+        <v>2.381630465303347e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>2.39727413863355e-05</v>
+        <v>2.397274138633545e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>2.36858266852805e-05</v>
+        <v>2.368582668528031e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>2.430603596053949e-05</v>
+        <v>2.430603596053948e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>2.353016449601586e-05</v>
+        <v>2.353016449601576e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>2.386669943162689e-05</v>
+        <v>2.386669943162681e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.370303016746905e-05</v>
+        <v>2.370303016746885e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.378962666412681e-05</v>
+        <v>2.378962666412683e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.384551862644773e-05</v>
+        <v>2.384551862644756e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.361016417082619e-05</v>
+        <v>2.361016417082604e-05</v>
       </c>
     </row>
     <row r="8">
@@ -1114,85 +1114,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.423185397166924e-05</v>
+        <v>2.423185397166913e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.429666744022806e-05</v>
+        <v>2.429666744022782e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.428089564627187e-05</v>
+        <v>2.428089564627157e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>2.262561015324712e-05</v>
+        <v>2.262561015324685e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.42868626916426e-05</v>
+        <v>2.428686269164232e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.415415236218359e-05</v>
+        <v>2.415415236218351e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.426029797404393e-05</v>
+        <v>2.426029797404381e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.426613988354936e-05</v>
+        <v>2.426613988354946e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.415883309600206e-05</v>
+        <v>2.415883309600164e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.423139787318099e-05</v>
+        <v>2.423139787318077e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>2.425379813064649e-05</v>
+        <v>2.425379813064654e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>2.419336719135197e-05</v>
+        <v>2.419336719135189e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>2.425287874759367e-05</v>
+        <v>2.425287874759336e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>2.421052879182895e-05</v>
+        <v>2.421052879182859e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>2.422887301707347e-05</v>
+        <v>2.422887301707345e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.426522731621351e-05</v>
+        <v>2.426522731621337e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>2.428802180573953e-05</v>
+        <v>2.428802180573929e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>2.422311117285985e-05</v>
+        <v>2.422311117285978e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>2.426909777461359e-05</v>
+        <v>2.426909777461352e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>2.418604913377762e-05</v>
+        <v>2.418604913377731e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>2.475306919038658e-05</v>
+        <v>2.475306919038655e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>2.414196379414089e-05</v>
+        <v>2.414196379414071e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>2.423878317791161e-05</v>
+        <v>2.423878317791162e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.419154892362898e-05</v>
+        <v>2.419154892362863e-05</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.421523373915696e-05</v>
+        <v>2.421523373915663e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.423211659481139e-05</v>
+        <v>2.423211659481125e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.416597607026358e-05</v>
+        <v>2.416597607026347e-05</v>
       </c>
     </row>
   </sheetData>
@@ -1358,16 +1358,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.490512864824332e-05</v>
+        <v>2.490512864824333e-05</v>
       </c>
       <c r="C2" t="n">
         <v>2.481603198014598e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>2.499487125927661e-05</v>
+        <v>2.49948712592766e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>2.303462492517765e-05</v>
+        <v>2.303462492517763e-05</v>
       </c>
       <c r="F2" t="n">
         <v>2.483960508605044e-05</v>
@@ -1376,67 +1376,67 @@
         <v>2.503601040800095e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>2.492467496430006e-05</v>
+        <v>2.492467496430001e-05</v>
       </c>
       <c r="I2" t="n">
         <v>2.49713729066122e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>2.490850631567514e-05</v>
+        <v>2.49085063156751e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>2.487959166647961e-05</v>
+        <v>2.487959166647959e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>2.488465367461366e-05</v>
+        <v>2.488465367461363e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>2.502623934752876e-05</v>
+        <v>2.502623934752875e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>2.486344048393517e-05</v>
+        <v>2.486344048393516e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>2.484102988426538e-05</v>
+        <v>2.484102988426537e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>2.482322420612048e-05</v>
+        <v>2.482322420612047e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.488614927972384e-05</v>
+        <v>2.488614927972386e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>2.49268300153086e-05</v>
+        <v>2.492683001530858e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>2.487640274672995e-05</v>
+        <v>2.487640274672992e-05</v>
       </c>
       <c r="T2" t="n">
         <v>2.49033290254013e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>2.487502618742487e-05</v>
+        <v>2.487502618742484e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>2.551615638088919e-05</v>
+        <v>2.551615638088911e-05</v>
       </c>
       <c r="W2" t="n">
         <v>2.50842421540009e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>2.484358960467184e-05</v>
+        <v>2.484358960467181e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.498670286110092e-05</v>
+        <v>2.498670286110089e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.488681689820936e-05</v>
+        <v>2.488681689820938e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.494930945391159e-05</v>
+        <v>2.494930945391157e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.50136586263648e-05</v>
+        <v>2.501365862636481e-05</v>
       </c>
     </row>
     <row r="3">
@@ -1455,7 +1455,7 @@
         <v>2.462635991146984e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>2.289332447264344e-05</v>
+        <v>2.289332447264341e-05</v>
       </c>
       <c r="F3" t="n">
         <v>2.462635991146984e-05</v>
@@ -1506,7 +1506,7 @@
         <v>2.462635991146984e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>2.522987308599617e-05</v>
+        <v>2.522987308599604e-05</v>
       </c>
       <c r="W3" t="n">
         <v>2.462635991146984e-05</v>
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0002028556464992017</v>
+        <v>0.000202855646499202</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0002056663287151533</v>
+        <v>0.0002056663287151535</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0002466208303597168</v>
+        <v>0.0002466208303597169</v>
       </c>
       <c r="E4" t="n">
-        <v>8.585372645257196e-05</v>
+        <v>8.585372645257203e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0002014132326809233</v>
+        <v>0.000201413232680923</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0002510537470132356</v>
+        <v>0.0002510537470132351</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0002241412719011054</v>
+        <v>0.0002241412719011053</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0002317254377456077</v>
+        <v>0.0002317254377456094</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0002268950702349719</v>
+        <v>0.0002268950702349718</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0002432875673522579</v>
+        <v>0.0002432875673522577</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0002229809534649922</v>
+        <v>0.0002229809534649923</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0002611695103207637</v>
+        <v>0.0002611695103207634</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0001863512412236642</v>
+        <v>0.0001863512412236643</v>
       </c>
       <c r="O4" t="n">
         <v>0.0001978128754603833</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0001878299695080604</v>
+        <v>0.0001878299695080603</v>
       </c>
       <c r="Q4" t="n">
         <v>0.0002094300540638166</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0002152863269838472</v>
+        <v>0.0002152863269838468</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0002046311326059069</v>
+        <v>0.0002046311326059067</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0002058159782439277</v>
+        <v>0.0002058159782439274</v>
       </c>
       <c r="U4" t="n">
         <v>0.0002240145990519534</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0002244073735308591</v>
+        <v>0.000224407373530859</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0002428471535208287</v>
+        <v>0.0002428471535208289</v>
       </c>
       <c r="X4" t="n">
-        <v>0.000202097936084032</v>
+        <v>0.0002020979360840312</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.000216293123835042</v>
+        <v>0.0002162931238350419</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0002132278544057742</v>
+        <v>0.0002132278544057741</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.000206067073695774</v>
+        <v>0.0002060670736957739</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0002479734084943377</v>
+        <v>0.0002479734084943381</v>
       </c>
     </row>
     <row r="5">
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0002317540127858694</v>
+        <v>0.0002317540127858691</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0003753994046666737</v>
+        <v>0.0003753994046666743</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0003753994046666737</v>
+        <v>0.0003753994046666743</v>
       </c>
       <c r="E5" t="n">
         <v>0.0002989124707590956</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0002541322860247495</v>
+        <v>0.0002541322860247491</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0004051852124376694</v>
+        <v>0.0004051852124376693</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0003753994046666737</v>
+        <v>0.0003753994046666743</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0003753994046666737</v>
+        <v>0.0003753994046666743</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0003753338550845473</v>
+        <v>0.0003753338550845469</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0003753994046666737</v>
+        <v>0.0003753994046666743</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0003753994046666737</v>
+        <v>0.0003753994046666743</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0003753994046666723</v>
+        <v>0.0003753994046666721</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0001863512412236642</v>
+        <v>0.0002640501946150034</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0002946499243794348</v>
+        <v>0.0002946499243794353</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0002871491912196132</v>
+        <v>0.0002871491912196128</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0002035244147286047</v>
+        <v>0.0002035244147286053</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0003753994046666737</v>
+        <v>0.0003753994046666743</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0003753994046666737</v>
+        <v>0.0003753994046666743</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0003753994046666737</v>
+        <v>0.0003753994046666743</v>
       </c>
       <c r="U5" t="n">
         <v>0.000305294064014425</v>
       </c>
       <c r="V5" t="n">
-        <v>0.000335870750017656</v>
+        <v>0.0003358707500176562</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0003754276351273648</v>
+        <v>0.0003754276351273638</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0002166898003376754</v>
+        <v>0.0002166898003376762</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0005182331115378115</v>
+        <v>0.0005182331115378114</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.000229085725881958</v>
+        <v>0.0002290857258819579</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0003753994046666737</v>
+        <v>0.0003753994046666743</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0005254490279418425</v>
+        <v>0.0005254490279418429</v>
       </c>
     </row>
     <row r="6">
@@ -1710,85 +1710,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0001285917967052312</v>
+        <v>0.000128591796705231</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0001625839286394476</v>
+        <v>0.000162583928639447</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001625839286394476</v>
+        <v>0.000162583928639447</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0001547386842308706</v>
+        <v>0.0001547386842308704</v>
       </c>
       <c r="F6" t="n">
-        <v>8.422278551736358e-05</v>
+        <v>8.422278551736344e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0001625839299270909</v>
+        <v>0.0001625839299270907</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0001625839286394476</v>
+        <v>0.000162583928639447</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0001625839286394476</v>
+        <v>0.000162583928639447</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0001625183790573199</v>
+        <v>0.0001625183790573197</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0001625839286394476</v>
+        <v>0.000162583928639447</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001625839286394476</v>
+        <v>0.000162583928639447</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0001625839286394476</v>
+        <v>0.000162583928639447</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0001863512412236642</v>
+        <v>0.000162583928639447</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0001738488783679051</v>
+        <v>0.0001738488783679052</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0001762988113798215</v>
+        <v>0.0001762988113798214</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0001625839299270909</v>
+        <v>0.0001625839299270907</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0001625839286394476</v>
+        <v>0.000162583928639447</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0001625839286394476</v>
+        <v>0.000162583928639447</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0001625839286394476</v>
+        <v>0.000162583928639447</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0001625839286394476</v>
+        <v>0.000162583928639447</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0002015352349117661</v>
+        <v>0.0002015352349117659</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0001625839286394476</v>
+        <v>0.000162583928639447</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0001625839286394476</v>
+        <v>0.000162583928639447</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0001625839286394476</v>
+        <v>0.000162583928639447</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0001420896962927305</v>
+        <v>0.0001420896962927304</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0001625839286394476</v>
+        <v>0.000162583928639447</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0001625839286394476</v>
+        <v>0.000162583928639447</v>
       </c>
     </row>
     <row r="7">
@@ -1798,7 +1798,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.352145358973629e-05</v>
+        <v>2.352145358973625e-05</v>
       </c>
       <c r="C7" t="n">
         <v>2.406336084365053e-05</v>
@@ -1807,28 +1807,28 @@
         <v>2.301672848851812e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.21482364953795e-05</v>
+        <v>2.214823649537947e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.393089570707689e-05</v>
+        <v>2.393089570707691e-05</v>
       </c>
       <c r="G7" t="n">
         <v>2.274402220450936e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.343780038328419e-05</v>
+        <v>2.343780038328417e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.315760286408875e-05</v>
+        <v>2.315760286408874e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.321628641040536e-05</v>
+        <v>2.321628641040531e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>2.369031330400672e-05</v>
+        <v>2.369031330400671e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>2.365102709919399e-05</v>
+        <v>2.3651027099194e-05</v>
       </c>
       <c r="M7" t="n">
         <v>2.284075911306381e-05</v>
@@ -1837,40 +1837,40 @@
         <v>2.37819710076222e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>2.390170901820722e-05</v>
+        <v>2.390170901820724e-05</v>
       </c>
       <c r="P7" t="n">
         <v>2.400699371446005e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.36504199987499e-05</v>
+        <v>2.365041999874989e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>2.342106716314455e-05</v>
+        <v>2.342106716314451e-05</v>
       </c>
       <c r="S7" t="n">
         <v>2.369601877936755e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>2.355379057789474e-05</v>
+        <v>2.355379057789471e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>2.370677813827404e-05</v>
+        <v>2.370677813827406e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>2.401309912813874e-05</v>
+        <v>2.401309912813859e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>2.247509904742829e-05</v>
+        <v>2.247509904742828e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>2.390189700130839e-05</v>
+        <v>2.39018970013084e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.305372959009806e-05</v>
+        <v>2.305372959009803e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.363179251464562e-05</v>
+        <v>2.363179251464564e-05</v>
       </c>
       <c r="AA7" t="n">
         <v>2.32728155231669e-05</v>
@@ -1886,37 +1886,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.440239275072702e-05</v>
+        <v>2.4402392750727e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.455986561011666e-05</v>
+        <v>2.455986561011663e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.426248383224258e-05</v>
+        <v>2.426248383224257e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>2.269560752106806e-05</v>
+        <v>2.269560752106804e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.452316665673872e-05</v>
+        <v>2.452316665673871e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.417954075267957e-05</v>
+        <v>2.417954075267956e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.43838765912611e-05</v>
+        <v>2.438387659126106e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.430308376940282e-05</v>
+        <v>2.430308376940283e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.428566538102527e-05</v>
+        <v>2.428566538102522e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.445368747708038e-05</v>
+        <v>2.445368747708034e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>2.44408741368269e-05</v>
+        <v>2.444087413682688e-05</v>
       </c>
       <c r="M8" t="n">
         <v>2.42137852938819e-05</v>
@@ -1925,7 +1925,7 @@
         <v>2.44792408417767e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>2.451131141850552e-05</v>
+        <v>2.451131141850553e-05</v>
       </c>
       <c r="P8" t="n">
         <v>2.454141061267807e-05</v>
@@ -1934,37 +1934,37 @@
         <v>2.444209350930031e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>2.437841797378051e-05</v>
+        <v>2.437841797378047e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>2.445309456680212e-05</v>
+        <v>2.445309456680215e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>2.4415306560549e-05</v>
+        <v>2.441530656054899e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>2.445661355008753e-05</v>
+        <v>2.445661355008754e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>2.496252035243549e-05</v>
+        <v>2.496252035243546e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>2.410541160520041e-05</v>
+        <v>2.41054116052004e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>2.451395667182208e-05</v>
+        <v>2.451395667182206e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.427115105320129e-05</v>
+        <v>2.427115105320124e-05</v>
       </c>
       <c r="Z8" t="n">
         <v>2.44342855631561e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.433344244374373e-05</v>
+        <v>2.43334424437437e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.423134292138069e-05</v>
+        <v>2.42313429213807e-05</v>
       </c>
     </row>
   </sheetData>
@@ -2130,85 +2130,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.447052645186332e-05</v>
+        <v>2.447052645186388e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>2.442989231241816e-05</v>
+        <v>2.442989231241823e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>2.450003885629727e-05</v>
+        <v>2.450003885629737e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>2.279383252726335e-05</v>
+        <v>2.279383252726352e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>2.443691157203421e-05</v>
+        <v>2.443691157203427e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>2.451624541543132e-05</v>
+        <v>2.451624541543141e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>2.44501448785567e-05</v>
+        <v>2.445014487855675e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>2.444661716242962e-05</v>
+        <v>2.444661716242975e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>2.444603804015972e-05</v>
+        <v>2.444603804015986e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>2.447810130911511e-05</v>
+        <v>2.447810130911518e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>2.446173976100951e-05</v>
+        <v>2.446173976100998e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>2.448709913611219e-05</v>
+        <v>2.448709913611221e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>2.447274660986834e-05</v>
+        <v>2.447274660986843e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>2.445610169742713e-05</v>
+        <v>2.445610169742725e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>2.445513318374123e-05</v>
+        <v>2.445513318374136e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.446707718385814e-05</v>
+        <v>2.446707718385829e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>2.447746074698007e-05</v>
+        <v>2.447746074698018e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>2.447617114527073e-05</v>
+        <v>2.447617114527078e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>2.447569019848378e-05</v>
+        <v>2.447569019848393e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>2.449241594779811e-05</v>
+        <v>2.449241594779819e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>2.501576597711977e-05</v>
+        <v>2.501576597711984e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>2.452689491782401e-05</v>
+        <v>2.452689491782414e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>2.448061502118139e-05</v>
+        <v>2.448061502118168e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.449024463811708e-05</v>
+        <v>2.449024463811717e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.447993405558395e-05</v>
+        <v>2.447993405558426e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.4478774896659e-05</v>
+        <v>2.447877489665915e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.451346417641901e-05</v>
+        <v>2.451346417641904e-05</v>
       </c>
     </row>
     <row r="3">
@@ -2218,85 +2218,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.428865916389885e-05</v>
+        <v>2.428865916389898e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>2.428865916389885e-05</v>
+        <v>2.428865916389898e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>2.428865916389885e-05</v>
+        <v>2.428865916389898e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>2.271789670244407e-05</v>
+        <v>2.271789670244419e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>2.428865916389885e-05</v>
+        <v>2.428865916389898e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>2.428865916389885e-05</v>
+        <v>2.428865916389898e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>2.428865916389885e-05</v>
+        <v>2.428865916389898e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>2.428865916389885e-05</v>
+        <v>2.428865916389898e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>2.424881150949716e-05</v>
+        <v>2.424881150949724e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>2.428865916389885e-05</v>
+        <v>2.428865916389898e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>2.428865916389885e-05</v>
+        <v>2.428865916389898e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>2.428865916389885e-05</v>
+        <v>2.428865916389898e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>2.428865916389885e-05</v>
+        <v>2.428865916389898e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>2.428865916389885e-05</v>
+        <v>2.428865916389898e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>2.428865916389885e-05</v>
+        <v>2.428865916389898e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.428865916389885e-05</v>
+        <v>2.428865916389898e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>2.428865916389885e-05</v>
+        <v>2.428865916389898e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>2.428865916389885e-05</v>
+        <v>2.428865916389898e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>2.428865916389885e-05</v>
+        <v>2.428865916389898e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>2.428865916389885e-05</v>
+        <v>2.428865916389898e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>2.484458481215084e-05</v>
+        <v>2.484458481215097e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>2.428865916389885e-05</v>
+        <v>2.428865916389898e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>2.428865916389885e-05</v>
+        <v>2.428865916389898e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.428865916389885e-05</v>
+        <v>2.428865916389898e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.428865916389885e-05</v>
+        <v>2.428865916389898e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.428865916389885e-05</v>
+        <v>2.428865916389898e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.428865916389885e-05</v>
+        <v>2.428865916389898e-05</v>
       </c>
     </row>
     <row r="4">
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0001886482429449896</v>
+        <v>0.0001886482429449946</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0001893772803579479</v>
+        <v>0.0001893772803579482</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0001939911186406235</v>
+        <v>0.0001939911186406231</v>
       </c>
       <c r="E4" t="n">
-        <v>4.584055375004583e-05</v>
+        <v>4.584055375009145e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0001880191538634495</v>
+        <v>0.000188019153863452</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0001952801088043468</v>
+        <v>0.0001952801088043503</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0001907476041690056</v>
+        <v>0.000190747604169007</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0001800793168822901</v>
+        <v>0.0001800793168822911</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0001901343551931396</v>
+        <v>0.0001901343551931356</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0002177840353855272</v>
+        <v>0.0002177840353855323</v>
       </c>
       <c r="L4" t="n">
-        <v>0.000176827587564268</v>
+        <v>0.0001768275875644919</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0002011763425821978</v>
+        <v>0.0002011763425821974</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0001846379071554131</v>
+        <v>0.000184637907155417</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0001945877652908754</v>
+        <v>0.0001945877652908758</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0001726978017930223</v>
+        <v>0.0001726978017930318</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0001859796103048393</v>
+        <v>0.0001859796103048604</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0001905682887651201</v>
+        <v>0.0001905682887651206</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0001876689458174419</v>
+        <v>0.0001876689458174539</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0001901424437166664</v>
+        <v>0.00019014244371668</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0001913362974635413</v>
+        <v>0.0001913362974635426</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0002083358755938898</v>
+        <v>0.00020833587559389</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0001966217024926305</v>
+        <v>0.0001966217024926296</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0001916399528737349</v>
+        <v>0.0001916399528737564</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0001969809109859947</v>
+        <v>0.0001969809109859949</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0001840702766597139</v>
+        <v>0.000184070276659724</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0001870177991643135</v>
+        <v>0.0001870177991643298</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.000211396871469963</v>
+        <v>0.0002113968714699643</v>
       </c>
     </row>
     <row r="5">
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0002472219487791363</v>
+        <v>0.0002472219487791354</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0004009355574377461</v>
+        <v>0.0004009355574377452</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0004009355574377461</v>
+        <v>0.0004009355574377452</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0003190875950893305</v>
+        <v>0.0003190875950893298</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0002711687325226469</v>
+        <v>0.0002711687325226463</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0004328090755461195</v>
+        <v>0.0004328090755461184</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0004009355574377461</v>
+        <v>0.0004009355574377452</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0004009355574377461</v>
+        <v>0.0004009355574377452</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0004008702824401547</v>
+        <v>0.0004008702824401535</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0004009355574377461</v>
+        <v>0.0004009355574377452</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0004009355574377461</v>
+        <v>0.0004009355574377452</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0004009355574377408</v>
+        <v>0.0004009355574377394</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0001846379071554131</v>
+        <v>0.0002817817950080429</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0003145262835331098</v>
+        <v>0.000314526283533109</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0003064998181762748</v>
+        <v>0.0003064998181762745</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0002170137163286207</v>
+        <v>0.00021701371632862</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0004009355574377461</v>
+        <v>0.0004009355574377451</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0004009355574377461</v>
+        <v>0.0004009355574377452</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0004009355574377461</v>
+        <v>0.000400935557437745</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0003259091767937119</v>
+        <v>0.0003259091767937107</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0003586491481314455</v>
+        <v>0.0003586491481314446</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0004009657665941705</v>
+        <v>0.0004009657665941691</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0002311018740128154</v>
+        <v>0.0002311018740128145</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0005537680972325765</v>
+        <v>0.0005537680972325746</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0002443666395794221</v>
+        <v>0.0002443666395794217</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0004009355574377461</v>
+        <v>0.0004009355574377452</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0005615022750302162</v>
+        <v>0.0005615022750302154</v>
       </c>
     </row>
     <row r="6">
@@ -2482,85 +2482,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0001508299131444326</v>
+        <v>0.0001508299131444328</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0001910766000856587</v>
+        <v>0.0001910766000856583</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001910766000856587</v>
+        <v>0.0001910766000856583</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0001817878298423976</v>
+        <v>0.0001817878298423978</v>
       </c>
       <c r="F6" t="n">
-        <v>9.82970007288281e-05</v>
+        <v>9.829700072882813e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0001910766013070895</v>
+        <v>0.0001910766013070896</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0001910766000856587</v>
+        <v>0.0001910766000856583</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0001910766000856587</v>
+        <v>0.0001910766000856583</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0001910113250880669</v>
+        <v>0.000191011325088067</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0001910766000856587</v>
+        <v>0.0001910766000856583</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001910766000856587</v>
+        <v>0.0001910766000856583</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0001910766000856587</v>
+        <v>0.0001910766000856583</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0001846379071554131</v>
+        <v>0.0001910766000856583</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0002044143010656408</v>
+        <v>0.0002044143010656409</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0002073150219267426</v>
+        <v>0.0002073150219267429</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0001910766013070895</v>
+        <v>0.0001910766013070896</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0001910766000856587</v>
+        <v>0.0001910766000856583</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0001910766000856587</v>
+        <v>0.0001910766000856583</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0001910766000856587</v>
+        <v>0.0001910766000856583</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0001910766000856587</v>
+        <v>0.0001910766000856583</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0002372471568114898</v>
+        <v>0.0002372471568114902</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0001910766000856587</v>
+        <v>0.0001910766000856583</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0001910766000856587</v>
+        <v>0.0001910766000856583</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0001910766000856587</v>
+        <v>0.0001910766000856583</v>
       </c>
       <c r="Z6" t="n">
         <v>0.0001668114272201538</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0001910766000856587</v>
+        <v>0.0001910766000856583</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0001910766000856587</v>
+        <v>0.0001910766000856583</v>
       </c>
     </row>
     <row r="7">
@@ -2570,85 +2570,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.37758627388846e-05</v>
+        <v>2.377586273888364e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>2.40251230308067e-05</v>
+        <v>2.402512303080684e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.361481474362613e-05</v>
+        <v>2.361481474362632e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.235998719774087e-05</v>
+        <v>2.235998719774009e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.398734201646539e-05</v>
+        <v>2.398734201646551e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.350446870135834e-05</v>
+        <v>2.35044687013584e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.39114555556025e-05</v>
+        <v>2.391145555560261e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.392888593690999e-05</v>
+        <v>2.392888593691009e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.363603944003139e-05</v>
+        <v>2.363603944003148e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>2.374219733972899e-05</v>
+        <v>2.374219733972912e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>2.383262026033032e-05</v>
+        <v>2.383262026032652e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>2.369384302708192e-05</v>
+        <v>2.369384302708206e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>2.377144149496289e-05</v>
+        <v>2.377144149496303e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>2.386092200084421e-05</v>
+        <v>2.386092200084433e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>2.386610522480304e-05</v>
+        <v>2.38661052248031e-05</v>
       </c>
       <c r="Q7" t="n">
         <v>2.380599634211444e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>2.375021313088121e-05</v>
+        <v>2.375021313088131e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>2.374475404685074e-05</v>
+        <v>2.374475404685007e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>2.375794399604584e-05</v>
+        <v>2.375794399604552e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>2.365038316822468e-05</v>
+        <v>2.365038316822474e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>2.43318709480235e-05</v>
+        <v>2.433187094802358e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>2.344924764513363e-05</v>
+        <v>2.344924764513368e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>2.372777932133095e-05</v>
+        <v>2.372777932133046e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.3666974405178e-05</v>
+        <v>2.366697440517812e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.372082102077036e-05</v>
+        <v>2.372082102077018e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.373394797034356e-05</v>
+        <v>2.373394797034348e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.35362703664513e-05</v>
+        <v>2.35362703664515e-05</v>
       </c>
     </row>
     <row r="8">
@@ -2658,85 +2658,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.42372024442966e-05</v>
+        <v>2.423720244429681e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.430998253202139e-05</v>
+        <v>2.430998253202151e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.419343749765846e-05</v>
+        <v>2.419343749765858e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>2.263098256203347e-05</v>
+        <v>2.263098256203336e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.42998113097112e-05</v>
+        <v>2.429981130971125e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.415943625590868e-05</v>
+        <v>2.415943625590878e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.427851603470529e-05</v>
+        <v>2.427851603470533e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.428291919762044e-05</v>
+        <v>2.428291919762051e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.416722479576408e-05</v>
+        <v>2.416722479576415e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.422945943764731e-05</v>
+        <v>2.422945943764736e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>2.425424060657609e-05</v>
+        <v>2.425424060657639e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>2.42164558982939e-05</v>
+        <v>2.421645589829404e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>2.423741092222756e-05</v>
+        <v>2.423741092222764e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>2.426147992511977e-05</v>
+        <v>2.426147992511989e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>2.426286979485314e-05</v>
+        <v>2.426286979485325e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.424746406179109e-05</v>
+        <v>2.424746406179113e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>2.423246608603136e-05</v>
+        <v>2.423246608603138e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>2.422869258369107e-05</v>
+        <v>2.422869258369103e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>2.423421310582177e-05</v>
+        <v>2.423421310582178e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>2.420199833570144e-05</v>
+        <v>2.420199833570158e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>2.47824795350197e-05</v>
+        <v>2.478247953501977e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>2.414496000174007e-05</v>
+        <v>2.414496000174009e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>2.422541290539498e-05</v>
+        <v>2.422541290539483e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.420737609170732e-05</v>
+        <v>2.420737609170743e-05</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.422156589086771e-05</v>
+        <v>2.422156589086797e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.422637953583163e-05</v>
+        <v>2.422637953583179e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.417112487585953e-05</v>
+        <v>2.417112487585962e-05</v>
       </c>
     </row>
   </sheetData>
@@ -2902,43 +2902,43 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.461668545005735e-05</v>
+        <v>2.461668545005737e-05</v>
       </c>
       <c r="C2" t="n">
         <v>2.457942010891394e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>2.465970245480243e-05</v>
+        <v>2.465970245480247e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>2.290005485436975e-05</v>
+        <v>2.290005485436977e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>2.457222565645191e-05</v>
+        <v>2.457222565645192e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>2.464873420833609e-05</v>
+        <v>2.464873420833611e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>2.459225633397754e-05</v>
+        <v>2.459225633397756e-05</v>
       </c>
       <c r="I2" t="n">
         <v>2.464160597704228e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>2.458548847751159e-05</v>
+        <v>2.458548847751151e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>2.465694518331459e-05</v>
+        <v>2.465694518331458e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>2.460429631842112e-05</v>
+        <v>2.460429631842113e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>2.463563729536097e-05</v>
+        <v>2.463563729536095e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>2.460532089286501e-05</v>
+        <v>2.460532089286502e-05</v>
       </c>
       <c r="O2" t="n">
         <v>2.457539732300368e-05</v>
@@ -2950,37 +2950,37 @@
         <v>2.459919903242952e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>2.460567244701598e-05</v>
+        <v>2.460567244701597e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>2.461956678112508e-05</v>
+        <v>2.46195667811251e-05</v>
       </c>
       <c r="T2" t="n">
         <v>2.462250113574383e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>2.461099854538161e-05</v>
+        <v>2.46109985453816e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>2.51682967919387e-05</v>
+        <v>2.516829679193879e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>2.468654332697608e-05</v>
+        <v>2.468654332697612e-05</v>
       </c>
       <c r="X2" t="n">
         <v>2.461152782222148e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.459776241157372e-05</v>
+        <v>2.459776241157373e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.462774806127224e-05</v>
+        <v>2.462774806127226e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.462928506619213e-05</v>
+        <v>2.462928506619216e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.465058723917516e-05</v>
+        <v>2.46505872391752e-05</v>
       </c>
     </row>
     <row r="3">
@@ -2990,85 +2990,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.440887051211612e-05</v>
+        <v>2.440887051211613e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>2.440887051211612e-05</v>
+        <v>2.440887051211613e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>2.440887051211612e-05</v>
+        <v>2.440887051211613e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>2.278747009205407e-05</v>
+        <v>2.27874700920541e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>2.440887051211612e-05</v>
+        <v>2.440887051211613e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>2.440887051211612e-05</v>
+        <v>2.440887051211613e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>2.440887051211612e-05</v>
+        <v>2.440887051211613e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>2.440887051211612e-05</v>
+        <v>2.440887051211613e-05</v>
       </c>
       <c r="J3" t="n">
         <v>2.436875594199441e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>2.440887051211612e-05</v>
+        <v>2.440887051211613e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>2.440887051211612e-05</v>
+        <v>2.440887051211613e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>2.440887051211612e-05</v>
+        <v>2.440887051211613e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>2.440887051211612e-05</v>
+        <v>2.440887051211613e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>2.440887051211612e-05</v>
+        <v>2.440887051211613e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>2.440887051211612e-05</v>
+        <v>2.440887051211613e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.440887051211612e-05</v>
+        <v>2.440887051211613e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>2.440887051211612e-05</v>
+        <v>2.440887051211613e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>2.440887051211612e-05</v>
+        <v>2.440887051211613e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>2.440887051211612e-05</v>
+        <v>2.440887051211613e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>2.440887051211612e-05</v>
+        <v>2.440887051211613e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>2.498013315054425e-05</v>
+        <v>2.498013315054424e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>2.440887051211612e-05</v>
+        <v>2.440887051211613e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>2.440887051211612e-05</v>
+        <v>2.440887051211613e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.440887051211612e-05</v>
+        <v>2.440887051211613e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.440887051211612e-05</v>
+        <v>2.440887051211613e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.440887051211612e-05</v>
+        <v>2.440887051211613e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.440887051211612e-05</v>
+        <v>2.440887051211613e-05</v>
       </c>
     </row>
     <row r="4">
@@ -3078,22 +3078,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0001772437871274894</v>
+        <v>0.0001772437871274901</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0001973987685308578</v>
+        <v>0.0001973987685308579</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0001959974051469249</v>
+        <v>0.000195997405146925</v>
       </c>
       <c r="E4" t="n">
-        <v>5.125304921170041e-05</v>
+        <v>5.12530492117004e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0001834623283580665</v>
+        <v>0.0001834623283580667</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0001921066277553701</v>
+        <v>0.00019210662775537</v>
       </c>
       <c r="H4" t="n">
         <v>0.0001815353258302078</v>
@@ -3102,34 +3102,34 @@
         <v>0.0001904141345039537</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0001877715641536749</v>
+        <v>0.0001877715641536751</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0002348063026577841</v>
+        <v>0.000234806302657784</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0001733131661232492</v>
+        <v>0.0001733131661232491</v>
       </c>
       <c r="M4" t="n">
         <v>0.0001949906771975275</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0001756181141486112</v>
+        <v>0.0001756181141486111</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0001849784713573644</v>
+        <v>0.0001849784713573647</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0001664627045670843</v>
+        <v>0.000166462704567084</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.000182038237232711</v>
+        <v>0.0001820382372327107</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0001805794179886751</v>
+        <v>0.0001805794179886753</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0001833915915988238</v>
+        <v>0.000183391591598824</v>
       </c>
       <c r="T4" t="n">
         <v>0.0001840255410460998</v>
@@ -3138,25 +3138,25 @@
         <v>0.000183315059264121</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0002035786082480168</v>
+        <v>0.0002035786082480265</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0001938716729276661</v>
+        <v>0.0001938716729276626</v>
       </c>
       <c r="X4" t="n">
         <v>0.0001834504402418469</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0001798316954744234</v>
+        <v>0.0001798316954744239</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.00019486935501156</v>
+        <v>0.0001948693550115599</v>
       </c>
       <c r="AA4" t="n">
         <v>0.0001815549819726035</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0002016616944105734</v>
+        <v>0.0002016616944105735</v>
       </c>
     </row>
     <row r="5">
@@ -3166,13 +3166,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0002311961244407154</v>
+        <v>0.0002311961244407155</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0003746036567713669</v>
+        <v>0.0003746036567713668</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0003746036567713669</v>
+        <v>0.0003746036567713668</v>
       </c>
       <c r="E5" t="n">
         <v>0.0002982433760577407</v>
@@ -3181,67 +3181,67 @@
         <v>0.0002535373419416744</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0004043401428151548</v>
+        <v>0.0004043401428151556</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0003746036567713669</v>
+        <v>0.0003746036567713668</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0003746036567713669</v>
+        <v>0.0003746036567713668</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0003745383705848207</v>
+        <v>0.0003745383705848205</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0003746036567713669</v>
+        <v>0.0003746036567713668</v>
       </c>
       <c r="L5" t="n">
-        <v>0.000374603656771367</v>
+        <v>0.0003746036567713668</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0003746036567713625</v>
+        <v>0.0003746036567713628</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0001756181141486112</v>
+        <v>0.0002634388276642375</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0002939878879443994</v>
+        <v>0.0002939878879443995</v>
       </c>
       <c r="P5" t="n">
         <v>0.0002864995750994921</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.00020301327121383</v>
+        <v>0.0002030132712138302</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0003746036567713669</v>
+        <v>0.0003746036567713668</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0003746036567713669</v>
+        <v>0.0003746036567713668</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0003746036567713669</v>
+        <v>0.0003746036567713668</v>
       </c>
       <c r="U5" t="n">
-        <v>0.000304610184985778</v>
+        <v>0.0003046101849857782</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0003351369774772422</v>
+        <v>0.0003351369774772421</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0003746318404863215</v>
+        <v>0.0003746318404863214</v>
       </c>
       <c r="X5" t="n">
-        <v>0.000216156856522783</v>
+        <v>0.0002161568565227833</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0005171936337874008</v>
+        <v>0.0005171936337874015</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0002285322559000415</v>
+        <v>0.0002285322559000417</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0003746036567713669</v>
+        <v>0.0003746036567713668</v>
       </c>
       <c r="AB5" t="n">
         <v>0.0005244048158573263</v>
@@ -3263,13 +3263,13 @@
         <v>0.0001691559189817224</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0001609728981407482</v>
+        <v>0.0001609728981407481</v>
       </c>
       <c r="F6" t="n">
-        <v>8.742094288511021e-05</v>
+        <v>8.742094288511031e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.000169155920281078</v>
+        <v>0.0001691559202810781</v>
       </c>
       <c r="H6" t="n">
         <v>0.0001691559189817224</v>
@@ -3278,7 +3278,7 @@
         <v>0.0001691559189817224</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0001690906327951763</v>
+        <v>0.0001690906327951764</v>
       </c>
       <c r="K6" t="n">
         <v>0.0001691559189817224</v>
@@ -3290,16 +3290,16 @@
         <v>0.0001691559189817224</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0001756181141486112</v>
+        <v>0.0001691559189817224</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0001809058802020619</v>
+        <v>0.0001809058802020617</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0001834612948895197</v>
+        <v>0.0001834612948895195</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.000169155920281078</v>
+        <v>0.0001691559202810781</v>
       </c>
       <c r="R6" t="n">
         <v>0.0001691559189817224</v>
@@ -3314,7 +3314,7 @@
         <v>0.0001691559189817224</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0002097977339916904</v>
+        <v>0.0002097977339916906</v>
       </c>
       <c r="W6" t="n">
         <v>0.0001691559189817224</v>
@@ -3342,34 +3342,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.373625808611304e-05</v>
+        <v>2.373625808611308e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>2.396804281427157e-05</v>
+        <v>2.396804281427155e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.349856918109623e-05</v>
+        <v>2.349856918109625e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.221209546764735e-05</v>
+        <v>2.221209546764737e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.40141826448232e-05</v>
+        <v>2.401418264482318e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.354623413764764e-05</v>
+        <v>2.354623413764763e-05</v>
       </c>
       <c r="H7" t="n">
         <v>2.389892387090317e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.36065518773965e-05</v>
+        <v>2.360655187739651e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.363789765828282e-05</v>
+        <v>2.363789765828279e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>2.351310811022228e-05</v>
+        <v>2.351310811022229e-05</v>
       </c>
       <c r="L7" t="n">
         <v>2.381531594975879e-05</v>
@@ -3378,7 +3378,7 @@
         <v>2.364341532409728e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>2.381354314672818e-05</v>
+        <v>2.381354314672822e-05</v>
       </c>
       <c r="O7" t="n">
         <v>2.398113214140347e-05</v>
@@ -3387,40 +3387,40 @@
         <v>2.397342894009372e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.385088519039857e-05</v>
+        <v>2.385088519039859e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>2.381840406911458e-05</v>
+        <v>2.381840406911459e-05</v>
       </c>
       <c r="S7" t="n">
         <v>2.372203195931292e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>2.37170856703243e-05</v>
+        <v>2.371708567032433e-05</v>
       </c>
       <c r="U7" t="n">
         <v>2.377481320091332e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>2.435960135813849e-05</v>
+        <v>2.435960135813831e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>2.333129718983005e-05</v>
+        <v>2.333129718983004e-05</v>
       </c>
       <c r="X7" t="n">
         <v>2.377987692773604e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.385658550616665e-05</v>
+        <v>2.385658550616666e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.367155844982156e-05</v>
+        <v>2.367155844982157e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.36700809549754e-05</v>
+        <v>2.367008095497542e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.355208055296441e-05</v>
+        <v>2.355208055296442e-05</v>
       </c>
     </row>
     <row r="8">
@@ -3430,85 +3430,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.431064465273734e-05</v>
+        <v>2.431064465273736e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.437884210156014e-05</v>
+        <v>2.437884210156016e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.424551244823018e-05</v>
+        <v>2.424551244823021e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>2.263825756665454e-05</v>
+        <v>2.263825756665456e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.439264141903801e-05</v>
+        <v>2.439264141903804e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.42562319088939e-05</v>
+        <v>2.425623190889392e-05</v>
       </c>
       <c r="H8" t="n">
         <v>2.436022898712214e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.42765484414071e-05</v>
+        <v>2.427654844140709e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.425294562931542e-05</v>
+        <v>2.425294562931555e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.424937043582745e-05</v>
+        <v>2.424937043582749e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>2.433422710100237e-05</v>
+        <v>2.433422710100239e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>2.428735274545146e-05</v>
+        <v>2.428735274545144e-05</v>
       </c>
       <c r="N8" t="n">
         <v>2.433444504441777e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>2.438077500120812e-05</v>
+        <v>2.438077500120811e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>2.437846330837345e-05</v>
+        <v>2.437846330837346e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.43453139328543e-05</v>
+        <v>2.434531393285432e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>2.433700833374537e-05</v>
+        <v>2.433700833374536e-05</v>
       </c>
       <c r="S8" t="n">
         <v>2.430705305077504e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>2.430773682814108e-05</v>
+        <v>2.430773682814109e-05</v>
       </c>
       <c r="U8" t="n">
         <v>2.432250044816359e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>2.488595284887661e-05</v>
+        <v>2.488595284887659e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>2.419624403131349e-05</v>
+        <v>2.419624403131352e-05</v>
       </c>
       <c r="X8" t="n">
         <v>2.432533373684494e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.434647097383885e-05</v>
+        <v>2.434647097383883e-05</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.429226872325409e-05</v>
+        <v>2.429226872325411e-05</v>
       </c>
       <c r="AA8" t="n">
         <v>2.42931334633105e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.426074507733356e-05</v>
+        <v>2.426074507733358e-05</v>
       </c>
     </row>
   </sheetData>
@@ -3674,85 +3674,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.468790056087231e-05</v>
+        <v>2.468790056087222e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>2.464772807820089e-05</v>
+        <v>2.464772807820108e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>2.477839391963956e-05</v>
+        <v>2.477839391963969e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>2.29393163994459e-05</v>
+        <v>2.293931639944578e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>2.464669418437226e-05</v>
+        <v>2.46466941843725e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>2.473250455045335e-05</v>
+        <v>2.473250455045337e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>2.468171465307892e-05</v>
+        <v>2.468171465307898e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>2.473228231574979e-05</v>
+        <v>2.473228231574995e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>2.466545191321504e-05</v>
+        <v>2.466545191321496e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>2.471505981005065e-05</v>
+        <v>2.471505981005072e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>2.466827982627338e-05</v>
+        <v>2.46682798262733e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>2.471547918174578e-05</v>
+        <v>2.47154791817459e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>2.466945850758179e-05</v>
+        <v>2.466945850758202e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>2.466489387230442e-05</v>
+        <v>2.466489387230473e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>2.465434294399479e-05</v>
+        <v>2.465434294399496e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.466227357498765e-05</v>
+        <v>2.466227357498773e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>2.467782069791069e-05</v>
+        <v>2.467782069791092e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>2.468268325277262e-05</v>
+        <v>2.468268325277299e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>2.470972169299495e-05</v>
+        <v>2.470972169299519e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>2.468450966537184e-05</v>
+        <v>2.468450966537203e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>2.526715409533353e-05</v>
+        <v>2.526715409533354e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>2.479512301495291e-05</v>
+        <v>2.479512301495313e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>2.467855962752896e-05</v>
+        <v>2.467855962752931e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.468296766601539e-05</v>
+        <v>2.468296766601532e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.470332055886236e-05</v>
+        <v>2.470332055886235e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.473026596717604e-05</v>
+        <v>2.473026596717637e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.473669098301696e-05</v>
+        <v>2.473669098301702e-05</v>
       </c>
     </row>
     <row r="3">
@@ -3762,85 +3762,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.447611742314722e-05</v>
+        <v>2.447611742314729e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>2.447611742314722e-05</v>
+        <v>2.447611742314729e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>2.447611742314722e-05</v>
+        <v>2.447611742314729e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>2.28184295505564e-05</v>
+        <v>2.281842955055656e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>2.447611742314722e-05</v>
+        <v>2.447611742314729e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>2.447611742314722e-05</v>
+        <v>2.447611742314729e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>2.447611742314722e-05</v>
+        <v>2.447611742314729e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>2.447611742314722e-05</v>
+        <v>2.447611742314729e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>2.443612432295335e-05</v>
+        <v>2.443612432295336e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>2.447611742314722e-05</v>
+        <v>2.447611742314729e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>2.447611742314722e-05</v>
+        <v>2.447611742314729e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>2.447611742314722e-05</v>
+        <v>2.447611742314729e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>2.447611742314722e-05</v>
+        <v>2.447611742314729e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>2.447611742314722e-05</v>
+        <v>2.447611742314729e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>2.447611742314722e-05</v>
+        <v>2.447611742314729e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.447611742314722e-05</v>
+        <v>2.447611742314729e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>2.447611742314722e-05</v>
+        <v>2.447611742314729e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>2.447611742314722e-05</v>
+        <v>2.447611742314729e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>2.447611742314722e-05</v>
+        <v>2.447611742314729e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>2.447611742314722e-05</v>
+        <v>2.447611742314729e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>2.506057255943695e-05</v>
+        <v>2.506057255943691e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>2.447611742314722e-05</v>
+        <v>2.447611742314729e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>2.447611742314722e-05</v>
+        <v>2.447611742314729e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.447611742314722e-05</v>
+        <v>2.447611742314729e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.447611742314722e-05</v>
+        <v>2.447611742314729e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.447611742314722e-05</v>
+        <v>2.447611742314729e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.447611742314722e-05</v>
+        <v>2.447611742314729e-05</v>
       </c>
     </row>
     <row r="4">
@@ -3853,82 +3853,82 @@
         <v>0.0001877590284274389</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0002004419777509583</v>
+        <v>0.0002004419777509587</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0002253578933014568</v>
+        <v>0.0002253578933014573</v>
       </c>
       <c r="E4" t="n">
-        <v>7.537484803325348e-05</v>
+        <v>7.537484803325375e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0001873618843189247</v>
+        <v>0.0001873618843189248</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0002090144692445133</v>
+        <v>0.0002090144692445072</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0001864730226391201</v>
+        <v>0.0001864730226391208</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0002041034237564221</v>
+        <v>0.0002041034237564225</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0002002825702596318</v>
+        <v>0.0002002825702596346</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0002316772003922252</v>
+        <v>0.0002316772003922259</v>
       </c>
       <c r="L4" t="n">
-        <v>0.000188332367524477</v>
+        <v>0.0001883323675244776</v>
       </c>
       <c r="M4" t="n">
-        <v>0.00021507183444956</v>
+        <v>0.0002150718344495601</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0001743834282481704</v>
+        <v>0.000174383428248171</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0001890492618362617</v>
+        <v>0.0001890492618362619</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0001810681437145071</v>
+        <v>0.0001810681437145068</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0001867478865715147</v>
+        <v>0.000186747886571515</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0001821432058939785</v>
+        <v>0.0001821432058939786</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0001859814319190592</v>
+        <v>0.0001859814319190593</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0001890227701161187</v>
+        <v>0.0001890227701161189</v>
       </c>
       <c r="U4" t="n">
-        <v>0.000198375328821776</v>
+        <v>0.0001983753288217757</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0002108955242920843</v>
+        <v>0.0002108955242920873</v>
       </c>
       <c r="W4" t="n">
         <v>0.000203937014658559</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0001918111909049883</v>
+        <v>0.0001918111909049884</v>
       </c>
       <c r="Y4" t="n">
         <v>0.0001764838774007131</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0002096525719557132</v>
+        <v>0.0002096525719557133</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0001880565403615728</v>
+        <v>0.000188056540361573</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.000210096428544182</v>
+        <v>0.0002100964285441819</v>
       </c>
     </row>
     <row r="5">
@@ -3938,34 +3938,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0002314141695197249</v>
+        <v>0.0002314141695197248</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0003749026952809309</v>
+        <v>0.0003749026952809308</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0003749026952809309</v>
+        <v>0.0003749026952809308</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0002984992879547104</v>
+        <v>0.0002984992879547113</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0002537680048505385</v>
+        <v>0.0002537680048505387</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0004046559758401608</v>
+        <v>0.0004046559758401612</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0003749026952809309</v>
+        <v>0.0003749026952809308</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0003749026952809309</v>
+        <v>0.0003749026952809308</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0003748374569697876</v>
+        <v>0.0003748374569697881</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0003749026952809309</v>
+        <v>0.0003749026952809308</v>
       </c>
       <c r="L5" t="n">
         <v>0.000374902695280931</v>
@@ -3974,49 +3974,49 @@
         <v>0.0003749026952809285</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0001743834282481704</v>
+        <v>0.0002636750827151579</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0002942413964348148</v>
+        <v>0.0002942413964348151</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0002867488543549944</v>
+        <v>0.0002867488543549945</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0002032153992351675</v>
+        <v>0.0002032153992351682</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0003749026952809309</v>
+        <v>0.0003749026952809308</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0003749026952809309</v>
+        <v>0.0003749026952809308</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0003749026952809309</v>
+        <v>0.0003749026952809308</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0003048732070495659</v>
+        <v>0.000304873207049566</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0003354181027179076</v>
+        <v>0.0003354181027179077</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0003749308949132482</v>
+        <v>0.0003749308949132479</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0002163664077528737</v>
+        <v>0.0002163664077528741</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.00051757921599119</v>
+        <v>0.0005175792159911897</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0002287487964844896</v>
+        <v>0.0002287487964844893</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0003749026952809309</v>
+        <v>0.0003749026952809308</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0005247884587775472</v>
+        <v>0.0005247884587775468</v>
       </c>
     </row>
     <row r="6">
@@ -4026,7 +4026,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.000127848020169286</v>
+        <v>0.0001278480201692862</v>
       </c>
       <c r="C6" t="n">
         <v>0.0001616601656535275</v>
@@ -4035,10 +4035,10 @@
         <v>0.0001616601656535275</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0001538564614734629</v>
+        <v>0.0001538564614734628</v>
       </c>
       <c r="F6" t="n">
-        <v>8.371394026886009e-05</v>
+        <v>8.371394026886035e-05</v>
       </c>
       <c r="G6" t="n">
         <v>0.0001616601670581873</v>
@@ -4050,25 +4050,25 @@
         <v>0.0001616601656535275</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0001615949273423849</v>
+        <v>0.0001615949273423847</v>
       </c>
       <c r="K6" t="n">
         <v>0.0001616601656535275</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001616601656535276</v>
+        <v>0.0001616601656535275</v>
       </c>
       <c r="M6" t="n">
         <v>0.0001616601656535275</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0001743834282481704</v>
+        <v>0.0001616601656535275</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0001728654682639309</v>
+        <v>0.0001728654682639313</v>
       </c>
       <c r="P6" t="n">
-        <v>0.000175302429025594</v>
+        <v>0.0001753024290255941</v>
       </c>
       <c r="Q6" t="n">
         <v>0.0001616601670581873</v>
@@ -4086,19 +4086,19 @@
         <v>0.0001616601656535275</v>
       </c>
       <c r="V6" t="n">
-        <v>0.000200405745330983</v>
+        <v>0.0002004057453309834</v>
       </c>
       <c r="W6" t="n">
         <v>0.0001616601656535275</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0001616601656535276</v>
+        <v>0.0001616601656535275</v>
       </c>
       <c r="Y6" t="n">
         <v>0.0001616601656535275</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0001412744491775921</v>
+        <v>0.0001412744491775919</v>
       </c>
       <c r="AA6" t="n">
         <v>0.0001616601656535275</v>
@@ -4114,85 +4114,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.377708254157252e-05</v>
+        <v>2.377708254157275e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>2.402629291721066e-05</v>
+        <v>2.402629291721063e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.326170682201961e-05</v>
+        <v>2.326170682201959e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.219448950133669e-05</v>
+        <v>2.219448950133685e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.403657760312802e-05</v>
+        <v>2.403657760312808e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.351242157229366e-05</v>
+        <v>2.351242157229411e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.383419182184736e-05</v>
+        <v>2.383419182184743e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.353405113833809e-05</v>
+        <v>2.353405113833831e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.363088909082376e-05</v>
+        <v>2.363088909082367e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>2.363114836293116e-05</v>
+        <v>2.363114836293107e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>2.389905845969712e-05</v>
+        <v>2.389905845969717e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>2.363440618441187e-05</v>
+        <v>2.363440618441198e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>2.389629690067665e-05</v>
+        <v>2.389629690067693e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>2.39130499205586e-05</v>
+        <v>2.391304992055888e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>2.397523307146953e-05</v>
+        <v>2.397523307146956e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.393985604259585e-05</v>
+        <v>2.393985604259579e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>2.385429420088083e-05</v>
+        <v>2.3854294200881e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>2.381096952920748e-05</v>
+        <v>2.381096952920742e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>2.366464120354466e-05</v>
+        <v>2.366464120354449e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>2.380219021167512e-05</v>
+        <v>2.380219021167519e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>2.432664501532427e-05</v>
+        <v>2.432664501532426e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>2.315180667516253e-05</v>
+        <v>2.315180667516257e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>2.384561116917254e-05</v>
+        <v>2.38456111691727e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.381522602407677e-05</v>
+        <v>2.38152260240767e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.368651807197473e-05</v>
+        <v>2.368651807197484e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.353560239278533e-05</v>
+        <v>2.353560239278524e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.350612766789568e-05</v>
+        <v>2.35061276678958e-05</v>
       </c>
     </row>
     <row r="8">
@@ -4202,85 +4202,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.436983746206337e-05</v>
+        <v>2.436983746206381e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.444305649449428e-05</v>
+        <v>2.444305649449425e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.42258332260295e-05</v>
+        <v>2.422583322602965e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>2.2655421688672e-05</v>
+        <v>2.265542168867187e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.444670216553329e-05</v>
+        <v>2.444670216553346e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.42940198671984e-05</v>
+        <v>2.429401986719869e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.43896364587919e-05</v>
+        <v>2.438963645879198e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.430363915397455e-05</v>
+        <v>2.430363915397471e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.429906731646361e-05</v>
+        <v>2.429906731646356e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.433059619489557e-05</v>
+        <v>2.433059619489567e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>2.440571615892574e-05</v>
+        <v>2.440571615892568e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>2.433249788574657e-05</v>
+        <v>2.433249788574672e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>2.440563832207983e-05</v>
+        <v>2.440563832207962e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>2.440869636423728e-05</v>
+        <v>2.440869636423733e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>2.442643896775766e-05</v>
+        <v>2.442643896775784e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.44182729378733e-05</v>
+        <v>2.441827293787313e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>2.439488915014657e-05</v>
+        <v>2.439488915014668e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>2.438003884132958e-05</v>
+        <v>2.438003884132977e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>2.434049742705433e-05</v>
+        <v>2.434049742705462e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>2.437787063647349e-05</v>
+        <v>2.437787063647365e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>2.493321472387399e-05</v>
+        <v>2.493321472387397e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>2.419255740429192e-05</v>
+        <v>2.419255740429209e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>2.439167727266668e-05</v>
+        <v>2.439167727266665e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.438225997330223e-05</v>
+        <v>2.438225997330226e-05</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.434405033777508e-05</v>
+        <v>2.434405033777504e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.43023286311182e-05</v>
+        <v>2.430232863111807e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.42953425532035e-05</v>
+        <v>2.429534255320366e-05</v>
       </c>
     </row>
   </sheetData>
@@ -4446,13 +4446,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.460712486146548e-05</v>
+        <v>2.460712486146551e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>2.451469510430235e-05</v>
+        <v>2.451469510430233e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>2.469045759627484e-05</v>
+        <v>2.469045759627482e-05</v>
       </c>
       <c r="E2" t="n">
         <v>2.283180478387346e-05</v>
@@ -4461,70 +4461,70 @@
         <v>2.45345863999974e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>2.463479421018339e-05</v>
+        <v>2.463479421018336e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>2.461019028049667e-05</v>
+        <v>2.46101902804966e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>2.454347361806255e-05</v>
+        <v>2.454347361806256e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>2.455032408570074e-05</v>
+        <v>2.455032408570078e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>2.458221761330395e-05</v>
+        <v>2.458221761330389e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>2.459439805985645e-05</v>
+        <v>2.45943980598564e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>2.457764405344321e-05</v>
+        <v>2.457764405344318e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>2.456473939212775e-05</v>
+        <v>2.456473939212771e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>2.454068959664662e-05</v>
+        <v>2.454068959664659e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>2.454252820079e-05</v>
+        <v>2.454252820078991e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.457910539186257e-05</v>
+        <v>2.457910539186254e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>2.458922739690113e-05</v>
+        <v>2.458922739690115e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>2.457532957688815e-05</v>
+        <v>2.457532957688811e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>2.457042943581674e-05</v>
+        <v>2.457042943581669e-05</v>
       </c>
       <c r="U2" t="n">
         <v>2.456788491915736e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>2.511938965773861e-05</v>
+        <v>2.51193896577385e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>2.463419991783417e-05</v>
+        <v>2.463419991783419e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>2.457239322622929e-05</v>
+        <v>2.457239322622928e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.457514543344226e-05</v>
+        <v>2.457514543344224e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.458573523817631e-05</v>
+        <v>2.458573523817633e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.45693101439509e-05</v>
+        <v>2.456931014395092e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.459911785708635e-05</v>
+        <v>2.459911785708638e-05</v>
       </c>
     </row>
     <row r="3">
@@ -4534,85 +4534,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.436910730151192e-05</v>
+        <v>2.436910730151188e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>2.436910730151192e-05</v>
+        <v>2.436910730151188e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>2.436910730151192e-05</v>
+        <v>2.436910730151188e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>2.275158285655709e-05</v>
+        <v>2.275158285655703e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>2.436910730151192e-05</v>
+        <v>2.436910730151188e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>2.436910730151192e-05</v>
+        <v>2.436910730151188e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>2.436910730151192e-05</v>
+        <v>2.436910730151188e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>2.436910730151192e-05</v>
+        <v>2.436910730151188e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>2.432863685949976e-05</v>
+        <v>2.432863685949969e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>2.436910730151192e-05</v>
+        <v>2.436910730151188e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>2.436910730151192e-05</v>
+        <v>2.436910730151188e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>2.436910730151192e-05</v>
+        <v>2.436910730151188e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>2.436910730151192e-05</v>
+        <v>2.436910730151188e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>2.436910730151192e-05</v>
+        <v>2.436910730151188e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>2.436910730151192e-05</v>
+        <v>2.436910730151188e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.436910730151192e-05</v>
+        <v>2.436910730151188e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>2.436910730151192e-05</v>
+        <v>2.436910730151188e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>2.436910730151192e-05</v>
+        <v>2.436910730151188e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>2.436910730151192e-05</v>
+        <v>2.436910730151188e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>2.436910730151192e-05</v>
+        <v>2.436910730151188e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>2.492837221482597e-05</v>
+        <v>2.492837221482588e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>2.436910730151192e-05</v>
+        <v>2.436910730151188e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>2.436910730151192e-05</v>
+        <v>2.436910730151188e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.436910730151192e-05</v>
+        <v>2.436910730151188e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.436910730151192e-05</v>
+        <v>2.436910730151188e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.436910730151192e-05</v>
+        <v>2.436910730151188e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.436910730151192e-05</v>
+        <v>2.436910730151188e-05</v>
       </c>
     </row>
     <row r="4">
@@ -4622,85 +4622,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0002065697301184815</v>
+        <v>0.0002065697301184812</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0001936240082808002</v>
+        <v>0.0001936240082807995</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0002322858034566318</v>
+        <v>0.0002322858034566319</v>
       </c>
       <c r="E4" t="n">
-        <v>4.722043160070557e-05</v>
+        <v>4.722043160070538e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0001988354521948356</v>
+        <v>0.0001988354521948354</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0002459216956772657</v>
+        <v>0.0002459216956772655</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0002162121396039294</v>
+        <v>0.0002162121396039289</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0001909978102496073</v>
+        <v>0.0001909978102496074</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0002195704078604639</v>
+        <v>0.0002195704078604637</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0002383783245189704</v>
+        <v>0.0002383783245189702</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0002426306243824636</v>
+        <v>0.0002426306243824633</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0002485288970030866</v>
+        <v>0.0002485288970030863</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0001955260791175433</v>
+        <v>0.000195526079117543</v>
       </c>
       <c r="O4" t="n">
         <v>0.0002023708867287625</v>
       </c>
       <c r="P4" t="n">
-        <v>0.000178873175736271</v>
+        <v>0.0001788731757362707</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0002068304297708702</v>
+        <v>0.00020683042977087</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0001999393390381682</v>
+        <v>0.0001999393390381678</v>
       </c>
       <c r="S4" t="n">
-        <v>0.000229991698014071</v>
+        <v>0.0002299916980140708</v>
       </c>
       <c r="T4" t="n">
-        <v>0.000218427343252901</v>
+        <v>0.0002184273432529012</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0002021289950844335</v>
+        <v>0.0002021289950844333</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0002155444478723161</v>
+        <v>0.0002155444478723159</v>
       </c>
       <c r="W4" t="n">
-        <v>0.000204362344819703</v>
+        <v>0.0002043623448197027</v>
       </c>
       <c r="X4" t="n">
         <v>0.000198254245808536</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0001995294630504377</v>
+        <v>0.0001995294630504374</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0002090091613455368</v>
+        <v>0.0002090091613455364</v>
       </c>
       <c r="AA4" t="n">
         <v>0.0001905734180332008</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0002227913945506748</v>
+        <v>0.0002227913945506746</v>
       </c>
     </row>
     <row r="5">
@@ -4713,82 +4713,82 @@
         <v>0.0002474081083077362</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0004011968447599488</v>
+        <v>0.0004011968447599481</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0004011968447599488</v>
+        <v>0.0004011968447599481</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0003193088790776445</v>
+        <v>0.0003193088790776446</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0002713665960834185</v>
+        <v>0.0002713665960834182</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0004330859411057159</v>
+        <v>0.0004330859411057156</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0004011968447599488</v>
+        <v>0.0004011968447599481</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0004011968447599488</v>
+        <v>0.0004011968447599481</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0004011313714724364</v>
+        <v>0.0004011313714724365</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0004011968447599488</v>
+        <v>0.0004011968447599481</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0004011968447599488</v>
+        <v>0.0004011968447599481</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0004011968447599426</v>
+        <v>0.0004011968447599419</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0001955260791175433</v>
+        <v>0.0002819848457215193</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0003147453381721501</v>
+        <v>0.0003147453381721493</v>
       </c>
       <c r="P5" t="n">
-        <v>0.000306714949866469</v>
+        <v>0.0003067149498664684</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0002171851115311666</v>
+        <v>0.0002171851115311659</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0004011968447599488</v>
+        <v>0.0004011968447599481</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0004011968447599488</v>
+        <v>0.0004011968447599481</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0004011968447599488</v>
+        <v>0.0004011968447599481</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0003261397605079186</v>
+        <v>0.0003261397605079182</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0003588952132635912</v>
+        <v>0.0003588952132635908</v>
       </c>
       <c r="W5" t="n">
-        <v>0.000401227068680807</v>
+        <v>0.0004012270686808059</v>
       </c>
       <c r="X5" t="n">
-        <v>0.000231280154826722</v>
+        <v>0.0002312801548267217</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0005541142872436037</v>
+        <v>0.0005541142872436027</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0002445514035707201</v>
+        <v>0.0002445514035707198</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0004011968447599488</v>
+        <v>0.0004011968447599481</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0005618420396146028</v>
+        <v>0.0005618420396146022</v>
       </c>
     </row>
     <row r="6">
@@ -4798,7 +4798,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0001512054095608164</v>
+        <v>0.0001512054095608163</v>
       </c>
       <c r="C6" t="n">
         <v>0.0001915371578482648</v>
@@ -4807,13 +4807,13 @@
         <v>0.0001915371578482648</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0001822287560783864</v>
+        <v>0.0001822287560783863</v>
       </c>
       <c r="F6" t="n">
-        <v>9.85614683891038e-05</v>
+        <v>9.856146838910382e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0001915371594403798</v>
+        <v>0.0001915371594403797</v>
       </c>
       <c r="H6" t="n">
         <v>0.0001915371578482648</v>
@@ -4834,16 +4834,16 @@
         <v>0.0001915371578482648</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0001955260791175433</v>
+        <v>0.0001915371578482648</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0002049030485405349</v>
+        <v>0.0002049030485405351</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0002078099000997883</v>
+        <v>0.0002078099000997882</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0001915371594403798</v>
+        <v>0.0001915371594403797</v>
       </c>
       <c r="R6" t="n">
         <v>0.0001915371578482648</v>
@@ -4858,7 +4858,7 @@
         <v>0.0001915371578482648</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0002378046059021222</v>
+        <v>0.0002378046059021221</v>
       </c>
       <c r="W6" t="n">
         <v>0.0001915371578482648</v>
@@ -4870,7 +4870,7 @@
         <v>0.0001915371578482648</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0001672207007021322</v>
+        <v>0.0001672207007021323</v>
       </c>
       <c r="AA6" t="n">
         <v>0.0001915371578482648</v>
@@ -4886,85 +4886,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.351890972880776e-05</v>
+        <v>2.351890972880777e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>2.40767288306982e-05</v>
+        <v>2.407672883069816e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.3047805240185e-05</v>
+        <v>2.304780524018497e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.236927546338014e-05</v>
+        <v>2.236927546338008e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.396409153517331e-05</v>
+        <v>2.396409153517318e-05</v>
       </c>
       <c r="G7" t="n">
         <v>2.335502386357834e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.352552542165417e-05</v>
+        <v>2.352552542165407e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.391010660550135e-05</v>
+        <v>2.391010660550131e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.356638809113203e-05</v>
+        <v>2.356638809113195e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>2.368050580246141e-05</v>
+        <v>2.368050580246136e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>2.360107809556023e-05</v>
+        <v>2.360107809556018e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>2.371208465692098e-05</v>
+        <v>2.371208465692096e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>2.378066496712962e-05</v>
+        <v>2.37806649671296e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>2.391335803272844e-05</v>
+        <v>2.391335803272836e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>2.390178328208911e-05</v>
+        <v>2.39017832820891e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.369768034181911e-05</v>
+        <v>2.369768034181905e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>2.364464667749872e-05</v>
+        <v>2.364464667749873e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>2.371089205849816e-05</v>
+        <v>2.371089205849806e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>2.37514354562447e-05</v>
+        <v>2.375143545624461e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>2.375696113662909e-05</v>
+        <v>2.375696113662913e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>2.429401156341005e-05</v>
+        <v>2.429401156340996e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>2.336786062034903e-05</v>
+        <v>2.3367860620349e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>2.373849279999937e-05</v>
+        <v>2.373849279999934e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.371786429102064e-05</v>
+        <v>2.371786429102063e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.364725687902095e-05</v>
+        <v>2.364725687902093e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.375158672109687e-05</v>
+        <v>2.375158672109691e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.358293321374563e-05</v>
+        <v>2.35829332137455e-05</v>
       </c>
     </row>
     <row r="8">
@@ -4974,85 +4974,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.422028225646618e-05</v>
+        <v>2.42202822564662e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.438166196832721e-05</v>
+        <v>2.438166196832718e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.40892609476313e-05</v>
+        <v>2.408926094763125e-05</v>
       </c>
       <c r="E8" t="n">
         <v>2.265785370163657e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.435030293560474e-05</v>
+        <v>2.435030293560464e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.417338301423145e-05</v>
+        <v>2.417338301423142e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.422635783682551e-05</v>
+        <v>2.422635783682552e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.433462683862935e-05</v>
+        <v>2.433462683862932e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.420349846695081e-05</v>
+        <v>2.420349846695075e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.426890173679316e-05</v>
+        <v>2.42689017367932e-05</v>
       </c>
       <c r="L8" t="n">
         <v>2.424494232358456e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>2.427869665634741e-05</v>
+        <v>2.427869665634739e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>2.429699625472936e-05</v>
+        <v>2.429699625472933e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>2.433332222696338e-05</v>
+        <v>2.433332222696336e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>2.432989428267931e-05</v>
+        <v>2.432989428267925e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.427360398549158e-05</v>
+        <v>2.427360398549161e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>2.425959550425612e-05</v>
+        <v>2.42595955042561e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>2.427583954370937e-05</v>
+        <v>2.427583954370938e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>2.428938677781684e-05</v>
+        <v>2.42893867778167e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>2.428935646334162e-05</v>
+        <v>2.428935646334164e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>2.48307535397569e-05</v>
+        <v>2.483075353975682e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>2.41786294871212e-05</v>
+        <v>2.417862948712119e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>2.428546161839195e-05</v>
+        <v>2.428546161839187e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.427882778828042e-05</v>
+        <v>2.427882778828039e-05</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.425729099554212e-05</v>
+        <v>2.425729099554213e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.428833631194083e-05</v>
+        <v>2.428833631194073e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.424140614176452e-05</v>
+        <v>2.424140614176453e-05</v>
       </c>
     </row>
   </sheetData>
@@ -5218,85 +5218,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.485222769593719e-05</v>
+        <v>2.485222769593711e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>2.475291077116287e-05</v>
+        <v>2.475291077116282e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>2.49488716060043e-05</v>
+        <v>2.494887160600426e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>2.302846032411204e-05</v>
+        <v>2.3028460324112e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>2.478120939544234e-05</v>
+        <v>2.478120939544224e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>2.490668481300157e-05</v>
+        <v>2.490668481300151e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>2.485627726529719e-05</v>
+        <v>2.485627726529715e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>2.489469760425864e-05</v>
+        <v>2.489469760425859e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>2.481874642488325e-05</v>
+        <v>2.481874642488316e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>2.494898906488873e-05</v>
+        <v>2.494898906488872e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>2.492331059827292e-05</v>
+        <v>2.49233105982729e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>2.492459550088173e-05</v>
+        <v>2.49245955008817e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>2.480073977004317e-05</v>
+        <v>2.480073977004311e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>2.475684195153727e-05</v>
+        <v>2.475684195153721e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>2.476738207756442e-05</v>
+        <v>2.476738207756441e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.483485793126054e-05</v>
+        <v>2.483485793126051e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>2.486101714673398e-05</v>
+        <v>2.486101714673399e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>2.482096292075139e-05</v>
+        <v>2.482096292075137e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>2.482442491844313e-05</v>
+        <v>2.482442491844309e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>2.481619000537526e-05</v>
+        <v>2.481619000537522e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>2.539536045778007e-05</v>
+        <v>2.539536045778009e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>2.489154325919096e-05</v>
+        <v>2.489154325919093e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>2.477994098591051e-05</v>
+        <v>2.477994098591046e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.486121533232801e-05</v>
+        <v>2.486121533232797e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.484083755285664e-05</v>
+        <v>2.484083755285661e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.488997467649739e-05</v>
+        <v>2.488997467649737e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.488303367884895e-05</v>
+        <v>2.488303367884892e-05</v>
       </c>
     </row>
     <row r="3">
@@ -5306,85 +5306,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.456892281517651e-05</v>
+        <v>2.456892281517643e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>2.456892281517651e-05</v>
+        <v>2.456892281517643e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>2.456892281517651e-05</v>
+        <v>2.456892281517643e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>2.287543109622728e-05</v>
+        <v>2.287543109622724e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>2.456892281517651e-05</v>
+        <v>2.456892281517643e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>2.456892281517651e-05</v>
+        <v>2.456892281517643e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>2.456892281517651e-05</v>
+        <v>2.456892281517643e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>2.456892281517651e-05</v>
+        <v>2.456892281517643e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>2.452780805296111e-05</v>
+        <v>2.452780805296112e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>2.456892281517651e-05</v>
+        <v>2.456892281517643e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>2.456892281517651e-05</v>
+        <v>2.456892281517643e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>2.456892281517651e-05</v>
+        <v>2.456892281517643e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>2.456892281517651e-05</v>
+        <v>2.456892281517643e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>2.456892281517651e-05</v>
+        <v>2.456892281517643e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>2.456892281517651e-05</v>
+        <v>2.456892281517643e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.456892281517651e-05</v>
+        <v>2.456892281517643e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>2.456892281517651e-05</v>
+        <v>2.456892281517643e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>2.456892281517651e-05</v>
+        <v>2.456892281517643e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>2.456892281517651e-05</v>
+        <v>2.456892281517643e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>2.456892281517651e-05</v>
+        <v>2.456892281517643e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>2.514821157626738e-05</v>
+        <v>2.514821157626725e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>2.456892281517651e-05</v>
+        <v>2.456892281517643e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>2.456892281517651e-05</v>
+        <v>2.456892281517643e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.456892281517651e-05</v>
+        <v>2.456892281517643e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.456892281517651e-05</v>
+        <v>2.456892281517643e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.456892281517651e-05</v>
+        <v>2.456892281517643e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.456892281517651e-05</v>
+        <v>2.456892281517643e-05</v>
       </c>
     </row>
     <row r="4">
@@ -5394,85 +5394,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0001990717357086535</v>
+        <v>0.000199071735708654</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0002041685836674296</v>
+        <v>0.0002041685836674295</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0002552492589948563</v>
+        <v>0.0002552492589948559</v>
       </c>
       <c r="E4" t="n">
-        <v>6.513821090860643e-05</v>
+        <v>6.513821090860614e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0002040678279688856</v>
+        <v>0.0002040678279688852</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0002555102038487894</v>
+        <v>0.0002555102038487905</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0002207579064409288</v>
+        <v>0.0002207579064409289</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0002303287651032611</v>
+        <v>0.0002303287651032605</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0002320606006989908</v>
+        <v>0.0002320606006989921</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0002706167156588448</v>
+        <v>0.0002706167156588447</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0002860887616869429</v>
+        <v>0.000286088761686942</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0002893224224615504</v>
+        <v>0.0002893224224615503</v>
       </c>
       <c r="N4" t="n">
         <v>0.0001962578656036421</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0001941700943114872</v>
+        <v>0.0001941700943114873</v>
       </c>
       <c r="P4" t="n">
         <v>0.0001795369655308899</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0002241714938349702</v>
+        <v>0.00022417149383497</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0002195712758494812</v>
+        <v>0.0002195712758494809</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0002213114125093595</v>
+        <v>0.0002213114125093596</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0002278323807887671</v>
+        <v>0.0002278323807887668</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0002428035328845594</v>
+        <v>0.0002428035328845591</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0002234829696108947</v>
+        <v>0.0002234829696108994</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0002285829976222275</v>
+        <v>0.0002285829976222268</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0002032856453341959</v>
+        <v>0.000203285645334196</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.000203715617555602</v>
+        <v>0.0002037156175556041</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.000210844226445244</v>
+        <v>0.0002108442264452438</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0002093542808229625</v>
+        <v>0.000209354280822963</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0002389471855389052</v>
+        <v>0.0002389471855389049</v>
       </c>
     </row>
     <row r="5">
@@ -5482,85 +5482,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0002315652207019418</v>
+        <v>0.0002315652207019411</v>
       </c>
       <c r="C5" t="n">
-        <v>0.000375128548487979</v>
+        <v>0.0003751285484879775</v>
       </c>
       <c r="D5" t="n">
-        <v>0.000375128548487979</v>
+        <v>0.0003751285484879775</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0002986853112901501</v>
+        <v>0.0002986853112901488</v>
       </c>
       <c r="F5" t="n">
-        <v>0.000253930709313972</v>
+        <v>0.0002539307093139708</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0004048973397343182</v>
+        <v>0.0004048973397343165</v>
       </c>
       <c r="H5" t="n">
-        <v>0.000375128548487979</v>
+        <v>0.0003751285484879775</v>
       </c>
       <c r="I5" t="n">
-        <v>0.000375128548487979</v>
+        <v>0.0003751285484879775</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0003750629841338163</v>
+        <v>0.0003750629841338149</v>
       </c>
       <c r="K5" t="n">
-        <v>0.000375128548487979</v>
+        <v>0.0003751285484879775</v>
       </c>
       <c r="L5" t="n">
-        <v>0.000375128548487979</v>
+        <v>0.0003751285484879775</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0003751285484879778</v>
+        <v>0.0003751285484879762</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0001962578656036421</v>
+        <v>0.00026384295183878</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0002944252000878334</v>
+        <v>0.0002944252000878321</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0002869287520698457</v>
+        <v>0.0002869287520698445</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0002033517501123649</v>
+        <v>0.0002033517501123641</v>
       </c>
       <c r="R5" t="n">
-        <v>0.000375128548487979</v>
+        <v>0.0003751285484879775</v>
       </c>
       <c r="S5" t="n">
-        <v>0.000375128548487979</v>
+        <v>0.0003751285484879775</v>
       </c>
       <c r="T5" t="n">
-        <v>0.000375128548487979</v>
+        <v>0.0003751285484879775</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0003050637902170716</v>
+        <v>0.0003050637902170705</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0003356227734230009</v>
+        <v>0.000335622773423</v>
       </c>
       <c r="W5" t="n">
-        <v>0.000375156762820673</v>
+        <v>0.0003751567628206716</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0002165096143840473</v>
+        <v>0.0002165096143840466</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.000517881564138248</v>
+        <v>0.0005178815641382464</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0002288984581807512</v>
+        <v>0.0002288984581807501</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.000375128548487979</v>
+        <v>0.0003751285484879775</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0005250924489539843</v>
+        <v>0.0005250924489539832</v>
       </c>
     </row>
     <row r="6">
@@ -5570,85 +5570,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0001344130134932322</v>
+        <v>0.0001344130134932321</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0001700315250481712</v>
+        <v>0.0001700315250481708</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001700315250481712</v>
+        <v>0.0001700315250481708</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0001618109189760522</v>
+        <v>0.0001618109189760517</v>
       </c>
       <c r="F6" t="n">
-        <v>8.792113281721121e-05</v>
+        <v>8.792113281721101e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0001700315264905709</v>
+        <v>0.0001700315264905707</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0001700315250481712</v>
+        <v>0.0001700315250481708</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0001700315250481712</v>
+        <v>0.0001700315250481708</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0001699659606940085</v>
+        <v>0.0001699659606940077</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0001700315250481712</v>
+        <v>0.0001700315250481708</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001700315250481712</v>
+        <v>0.0001700315250481708</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0001700315250481712</v>
+        <v>0.0001700315250481708</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0001962578656036421</v>
+        <v>0.0001700315250481708</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0001818354550594159</v>
+        <v>0.0001818354550594154</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0001844026070018376</v>
+        <v>0.0001844026070018373</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0001700315264905709</v>
+        <v>0.0001700315264905707</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0001700315250481712</v>
+        <v>0.0001700315250481708</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0001700315250481712</v>
+        <v>0.0001700315250481708</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0001700315250481712</v>
+        <v>0.0001700315250481708</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0001700315250481712</v>
+        <v>0.0001700315250481708</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0002108595070508935</v>
+        <v>0.0002108595070508934</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0001700315250481712</v>
+        <v>0.0001700315250481708</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0001700315250481712</v>
+        <v>0.0001700315250481708</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0001700315250481712</v>
+        <v>0.0001700315250481708</v>
       </c>
       <c r="Z6" t="n">
         <v>0.0001485567304749289</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0001700315250481712</v>
+        <v>0.0001700315250481708</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0001700315250481712</v>
+        <v>0.0001700315250481708</v>
       </c>
     </row>
     <row r="7">
@@ -5658,85 +5658,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.343960244552603e-05</v>
+        <v>2.343960244552597e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>2.404179237859137e-05</v>
+        <v>2.404179237859133e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.289482839030526e-05</v>
+        <v>2.28948283903052e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.205997821517834e-05</v>
+        <v>2.205997821517829e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.388156588453373e-05</v>
+        <v>2.388156588453367e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.311659531463168e-05</v>
+        <v>2.311659531463179e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.344664730845889e-05</v>
+        <v>2.344664730845883e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.321517060817752e-05</v>
+        <v>2.321517060817749e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.33500020286075e-05</v>
+        <v>2.335000202860746e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>2.289142167032616e-05</v>
+        <v>2.289142167032617e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>2.302805355580377e-05</v>
+        <v>2.30280535558037e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>2.304380424036337e-05</v>
+        <v>2.304380424036331e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>2.375803917394869e-05</v>
+        <v>2.375803917394866e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>2.400616567175494e-05</v>
+        <v>2.400616567175491e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>2.394262651328359e-05</v>
+        <v>2.394262651328351e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.355943067456887e-05</v>
+        <v>2.355943067456882e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>2.341502018778812e-05</v>
+        <v>2.341502018778805e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>2.362930048729952e-05</v>
+        <v>2.362930048729949e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>2.362454788970287e-05</v>
+        <v>2.362454788970286e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>2.36601789815026e-05</v>
+        <v>2.366017898150256e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>2.416872115062224e-05</v>
+        <v>2.416872115062216e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>2.32185253370477e-05</v>
+        <v>2.321852533704765e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>2.388341374862588e-05</v>
+        <v>2.388341374862584e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.339982333425385e-05</v>
+        <v>2.339982333425379e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.35088361554292e-05</v>
+        <v>2.350883615542916e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.322911890882078e-05</v>
+        <v>2.322911890882075e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.328069344914831e-05</v>
+        <v>2.328069344914829e-05</v>
       </c>
     </row>
     <row r="8">
@@ -5746,85 +5746,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.433838332881572e-05</v>
+        <v>2.433838332881568e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.451306474265163e-05</v>
+        <v>2.451306474265158e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.418715330766549e-05</v>
+        <v>2.418715330766545e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>2.265742666454065e-05</v>
+        <v>2.265742666454061e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.446845980152331e-05</v>
+        <v>2.446845980152323e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.42458711719605e-05</v>
+        <v>2.424587117196058e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.434563833326083e-05</v>
+        <v>2.434563833326078e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.42787360359218e-05</v>
+        <v>2.427873603592173e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.428284093035724e-05</v>
+        <v>2.428284093035716e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.418572069810289e-05</v>
+        <v>2.418572069810284e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>2.422221017479935e-05</v>
+        <v>2.422221017479934e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>2.423066168907726e-05</v>
+        <v>2.423066168907724e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>2.443178512915173e-05</v>
+        <v>2.443178512915164e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>2.450078565787986e-05</v>
+        <v>2.450078565787981e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>2.448241526431523e-05</v>
+        <v>2.44824152643152e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.437553579022351e-05</v>
+        <v>2.437553579022345e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>2.43359877740028e-05</v>
+        <v>2.433598777400273e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>2.439343176716875e-05</v>
+        <v>2.439343176716867e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>2.439473131780833e-05</v>
+        <v>2.439473131780829e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>2.440270866505886e-05</v>
+        <v>2.44027086650588e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>2.494968919266076e-05</v>
+        <v>2.494968919266083e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>2.427710810318096e-05</v>
+        <v>2.427710810318092e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>2.446803217604221e-05</v>
+        <v>2.446803217604213e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.432927134280923e-05</v>
+        <v>2.43292713428092e-05</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.435849474437588e-05</v>
+        <v>2.435849474437585e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.428035962940386e-05</v>
+        <v>2.428035962940378e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.429688521196275e-05</v>
+        <v>2.429688521196269e-05</v>
       </c>
     </row>
   </sheetData>
@@ -5990,85 +5990,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.505720151818233e-05</v>
+        <v>2.505720151818232e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>2.494245252660432e-05</v>
+        <v>2.494245252660428e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>2.511106068444969e-05</v>
+        <v>2.511106068444966e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>2.318461928971114e-05</v>
+        <v>2.318461928971115e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>2.496235804653166e-05</v>
+        <v>2.496235804653165e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>2.527767233214496e-05</v>
+        <v>2.527767233214495e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>2.505728863733475e-05</v>
+        <v>2.505728863733473e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>2.509220584259594e-05</v>
+        <v>2.509220584259592e-05</v>
       </c>
       <c r="J2" t="n">
         <v>2.506472945926144e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>2.515611638576816e-05</v>
+        <v>2.515611638576815e-05</v>
       </c>
       <c r="L2" t="n">
         <v>2.508351432113261e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>2.515879264210377e-05</v>
+        <v>2.515879264210374e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>2.499162736051105e-05</v>
+        <v>2.499162736051102e-05</v>
       </c>
       <c r="O2" t="n">
         <v>2.496036067590179e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>2.495341566344123e-05</v>
+        <v>2.495341566344121e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.502704989672332e-05</v>
+        <v>2.502704989672328e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>2.506049640591474e-05</v>
+        <v>2.506049640591471e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>2.498576619195609e-05</v>
+        <v>2.498576619195608e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>2.502685135549362e-05</v>
+        <v>2.50268513554936e-05</v>
       </c>
       <c r="U2" t="n">
         <v>2.499705949798549e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>2.561072662299888e-05</v>
+        <v>2.561072662299891e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>2.531980165531088e-05</v>
+        <v>2.531980165531086e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>2.496321466849429e-05</v>
+        <v>2.496321466849426e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.512674528072373e-05</v>
+        <v>2.512674528072371e-05</v>
       </c>
       <c r="Z2" t="n">
         <v>2.502351107470467e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.511781381071702e-05</v>
+        <v>2.5117813810717e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.508703131770562e-05</v>
+        <v>2.508703131770558e-05</v>
       </c>
     </row>
     <row r="3">
@@ -6078,85 +6078,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.473352309351971e-05</v>
+        <v>2.473352309351969e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>2.473352309351971e-05</v>
+        <v>2.473352309351969e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>2.473352309351971e-05</v>
+        <v>2.473352309351969e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>2.297653864155335e-05</v>
+        <v>2.297653864155331e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>2.473352309351971e-05</v>
+        <v>2.473352309351969e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>2.473352309351971e-05</v>
+        <v>2.473352309351969e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>2.473352309351971e-05</v>
+        <v>2.473352309351969e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>2.473352309351971e-05</v>
+        <v>2.473352309351969e-05</v>
       </c>
       <c r="J3" t="n">
         <v>2.468858636939051e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>2.473352309351971e-05</v>
+        <v>2.473352309351969e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>2.473352309351971e-05</v>
+        <v>2.473352309351969e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>2.473352309351971e-05</v>
+        <v>2.473352309351969e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>2.473352309351971e-05</v>
+        <v>2.473352309351969e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>2.473352309351971e-05</v>
+        <v>2.473352309351969e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>2.473352309351971e-05</v>
+        <v>2.473352309351969e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.473352309351971e-05</v>
+        <v>2.473352309351969e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>2.473352309351971e-05</v>
+        <v>2.473352309351969e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>2.473352309351971e-05</v>
+        <v>2.473352309351969e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>2.473352309351971e-05</v>
+        <v>2.473352309351969e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>2.473352309351971e-05</v>
+        <v>2.473352309351969e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>2.532009624842056e-05</v>
+        <v>2.53200962484206e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>2.473352309351971e-05</v>
+        <v>2.473352309351969e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>2.473352309351971e-05</v>
+        <v>2.473352309351969e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.473352309351971e-05</v>
+        <v>2.473352309351969e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.473352309351971e-05</v>
+        <v>2.473352309351969e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.473352309351971e-05</v>
+        <v>2.473352309351969e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.473352309351971e-05</v>
+        <v>2.473352309351969e-05</v>
       </c>
     </row>
     <row r="4">
@@ -6169,82 +6169,82 @@
         <v>0.0002115186872195174</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0002056314777486064</v>
+        <v>0.0002056314777486063</v>
       </c>
       <c r="D4" t="n">
         <v>0.000247144103085235</v>
       </c>
       <c r="E4" t="n">
-        <v>9.914899442229529e-05</v>
+        <v>9.914899442229527e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0002029240181385467</v>
+        <v>0.000202924018138547</v>
       </c>
       <c r="G4" t="n">
-        <v>0.000282346256441674</v>
+        <v>0.0002823462564416758</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0002345517327103325</v>
+        <v>0.0002345517327103328</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0002345515733404408</v>
+        <v>0.0002345515733404406</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0002416506042565861</v>
+        <v>0.0002416506042565876</v>
       </c>
       <c r="K4" t="n">
         <v>0.0002664471811113808</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0002632160051337325</v>
+        <v>0.0002632160051337324</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0002759153357096587</v>
+        <v>0.000275915335709659</v>
       </c>
       <c r="N4" t="n">
         <v>0.0001985928699513997</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0002007493244986583</v>
+        <v>0.0002007493244986582</v>
       </c>
       <c r="P4" t="n">
         <v>0.0001939485691536371</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0002194398032911112</v>
+        <v>0.0002194398032911113</v>
       </c>
       <c r="R4" t="n">
-        <v>0.000224484044546352</v>
+        <v>0.0002244840445463507</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0002068643416760268</v>
+        <v>0.0002068643416760271</v>
       </c>
       <c r="T4" t="n">
         <v>0.0002227306005995851</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0002324821299877264</v>
+        <v>0.0002324821299877265</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0002240879945384793</v>
+        <v>0.0002240879945384796</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0002857142872684001</v>
+        <v>0.0002857142872684004</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0002116321208200774</v>
+        <v>0.0002116321208200773</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0002250205773065873</v>
+        <v>0.000225020577306588</v>
       </c>
       <c r="Z4" t="n">
         <v>0.0002196910466480666</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0002243594388696693</v>
+        <v>0.0002243594388696696</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0002419438655007141</v>
+        <v>0.0002419438655007143</v>
       </c>
     </row>
     <row r="5">
@@ -6257,40 +6257,40 @@
         <v>0.0002319635838262683</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0003757207889944128</v>
+        <v>0.0003757207889944129</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0003757207889944128</v>
+        <v>0.0003757207889944129</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0002991743178096837</v>
+        <v>0.0002991743178096836</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0002543592762684887</v>
+        <v>0.0002543592762684889</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0004055297819789092</v>
+        <v>0.0004055297819789097</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0003757207889944128</v>
+        <v>0.0003757207889944129</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0003757207889944128</v>
+        <v>0.0003757207889944129</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0003756544573475986</v>
+        <v>0.0003756544573475989</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0003757207889944128</v>
+        <v>0.0003757207889944129</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0003757207889944128</v>
+        <v>0.0003757207889944129</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0003757207889944149</v>
+        <v>0.0003757207889944151</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0001985928699513998</v>
+        <v>0.0002642849049390126</v>
       </c>
       <c r="O5" t="n">
         <v>0.0002949084534720681</v>
@@ -6299,25 +6299,25 @@
         <v>0.0002874018817565312</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0002037120119061238</v>
+        <v>0.000203712011906124</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0003757207889944128</v>
+        <v>0.0003757207889944129</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0003757207889944128</v>
+        <v>0.0003757207889944129</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0003757207889944128</v>
+        <v>0.0003757207889944129</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0003055623579910921</v>
+        <v>0.0003055623579910925</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0003361582269580867</v>
+        <v>0.0003361582269580873</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0003757490414292743</v>
+        <v>0.0003757490414292744</v>
       </c>
       <c r="X5" t="n">
         <v>0.0002168876454249452</v>
@@ -6326,13 +6326,13 @@
         <v>0.0005186682083445912</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0002292932199331722</v>
+        <v>0.0002292932199331726</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0003757207889944128</v>
+        <v>0.0003757207889944129</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0005258872105975552</v>
+        <v>0.0005258872105975561</v>
       </c>
     </row>
     <row r="6">
@@ -6354,10 +6354,10 @@
         <v>0.000155333027039842</v>
       </c>
       <c r="F6" t="n">
-        <v>8.455185421258142e-05</v>
+        <v>8.455185421258149e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0001632077858052738</v>
+        <v>0.0001632077858052739</v>
       </c>
       <c r="H6" t="n">
         <v>0.0001632077841410827</v>
@@ -6366,7 +6366,7 @@
         <v>0.0001632077841410827</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0001631414524942684</v>
+        <v>0.0001631414524942682</v>
       </c>
       <c r="K6" t="n">
         <v>0.0001632077841410827</v>
@@ -6378,16 +6378,16 @@
         <v>0.0001632077841410827</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0001985928699513997</v>
+        <v>0.0001632077841410827</v>
       </c>
       <c r="O6" t="n">
         <v>0.0001745151119122408</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0001769742613394673</v>
+        <v>0.000176974261339467</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0001632077858052738</v>
+        <v>0.0001632077858052739</v>
       </c>
       <c r="R6" t="n">
         <v>0.0001632077841410827</v>
@@ -6402,7 +6402,7 @@
         <v>0.0001632077841410827</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0002023016713375943</v>
+        <v>0.0002023016713375945</v>
       </c>
       <c r="W6" t="n">
         <v>0.0001632077841410827</v>
@@ -6414,7 +6414,7 @@
         <v>0.0001632077841410827</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.000142636454810409</v>
+        <v>0.0001426364548104091</v>
       </c>
       <c r="AA6" t="n">
         <v>0.0001632077841410827</v>
@@ -6430,43 +6430,43 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.335593304193298e-05</v>
+        <v>2.335593304193297e-05</v>
       </c>
       <c r="C7" t="n">
         <v>2.405216359090517e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.306559750678802e-05</v>
+        <v>2.306559750678798e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.183337625444938e-05</v>
+        <v>2.183337625444936e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.394179090308148e-05</v>
+        <v>2.394179090308146e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.204596873845917e-05</v>
+        <v>2.204596873845903e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.339150605130019e-05</v>
+        <v>2.339150605130018e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.317943249374907e-05</v>
+        <v>2.317943249374906e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.300193447627782e-05</v>
+        <v>2.30019344762778e-05</v>
       </c>
       <c r="K7" t="n">
         <v>2.279859906986902e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>2.321061627119627e-05</v>
+        <v>2.321061627119628e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>2.279436139705638e-05</v>
+        <v>2.279436139705635e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>2.376002044822722e-05</v>
+        <v>2.376002044822721e-05</v>
       </c>
       <c r="O7" t="n">
         <v>2.393089189750356e-05</v>
@@ -6475,40 +6475,40 @@
         <v>2.397136748005997e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.355402314062897e-05</v>
+        <v>2.355402314062895e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>2.336819755491627e-05</v>
+        <v>2.336819755491626e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>2.378464156339191e-05</v>
+        <v>2.37846415633919e-05</v>
       </c>
       <c r="T7" t="n">
         <v>2.355977118805969e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>2.372046488237176e-05</v>
+        <v>2.372046488237174e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>2.40725165659478e-05</v>
+        <v>2.407251656594782e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>2.181900619725322e-05</v>
+        <v>2.181900619725319e-05</v>
       </c>
       <c r="X7" t="n">
         <v>2.393056616023555e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.296169843703356e-05</v>
+        <v>2.296169843703354e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.355796324810591e-05</v>
+        <v>2.355796324810589e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.301277917491407e-05</v>
+        <v>2.301277917491403e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.320662214870518e-05</v>
+        <v>2.320662214870517e-05</v>
       </c>
     </row>
     <row r="8">
@@ -6518,52 +6518,52 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.443039365459137e-05</v>
+        <v>2.443039365459136e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.46324317815508e-05</v>
+        <v>2.463243178155079e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.435214922712329e-05</v>
+        <v>2.435214922712327e-05</v>
       </c>
       <c r="E8" t="n">
         <v>2.266447676053648e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.46021173767815e-05</v>
+        <v>2.460211737678148e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.405482653586484e-05</v>
+        <v>2.405482653586481e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.444666660637033e-05</v>
+        <v>2.444666660637034e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.438508966710742e-05</v>
+        <v>2.438508966710741e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.429729747285449e-05</v>
+        <v>2.429729747285448e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.427571978877011e-05</v>
+        <v>2.42757197887701e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>2.439058686375937e-05</v>
+        <v>2.439058686375936e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>2.427646789047129e-05</v>
+        <v>2.427646789047126e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>2.454868055453412e-05</v>
+        <v>2.454868055453411e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>2.45951609238806e-05</v>
+        <v>2.459516092388059e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>2.460663243047121e-05</v>
+        <v>2.46066324304712e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.449037365931468e-05</v>
+        <v>2.449037365931467e-05</v>
       </c>
       <c r="R8" t="n">
         <v>2.443926893481584e-05</v>
@@ -6572,31 +6572,31 @@
         <v>2.455402207184192e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>2.449279049798391e-05</v>
+        <v>2.449279049798393e-05</v>
       </c>
       <c r="U8" t="n">
         <v>2.453611478348821e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>2.504307389167323e-05</v>
+        <v>2.504307389167325e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>2.399368717949536e-05</v>
+        <v>2.399368717949535e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>2.459786670497808e-05</v>
+        <v>2.459786670497806e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.432055941555239e-05</v>
+        <v>2.432055941555236e-05</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.448862759875446e-05</v>
+        <v>2.448862759875444e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.433486984406597e-05</v>
+        <v>2.433486984406593e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.439228652187038e-05</v>
+        <v>2.439228652187039e-05</v>
       </c>
     </row>
   </sheetData>
@@ -6762,85 +6762,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.449459049324448e-05</v>
+        <v>2.449459049324446e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>2.443929749042907e-05</v>
+        <v>2.443929749042901e-05</v>
       </c>
       <c r="D2" t="n">
         <v>2.452491848372473e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>2.280045224147645e-05</v>
+        <v>2.280045224147647e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>2.445200130848375e-05</v>
+        <v>2.445200130848378e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>2.452941023341615e-05</v>
+        <v>2.452941023341612e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>2.446569333740215e-05</v>
+        <v>2.446569333740209e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>2.446966563099322e-05</v>
+        <v>2.446966563099313e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>2.44535495759128e-05</v>
+        <v>2.445354957591273e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>2.449991055058281e-05</v>
+        <v>2.449991055058269e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>2.4474606016639e-05</v>
+        <v>2.447460601663893e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>2.449500109021726e-05</v>
+        <v>2.449500109021724e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>2.447119361519312e-05</v>
+        <v>2.447119361519318e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>2.447001618436912e-05</v>
+        <v>2.447001618436909e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>2.446726959527254e-05</v>
+        <v>2.446726959527255e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.447795458636744e-05</v>
+        <v>2.447795458636735e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>2.450532875262092e-05</v>
+        <v>2.450532875262088e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>2.447630776727451e-05</v>
+        <v>2.447630776727443e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>2.450375508497108e-05</v>
+        <v>2.450375508497099e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>2.449163656326194e-05</v>
+        <v>2.449163656326187e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>2.502639437314805e-05</v>
+        <v>2.502639437314808e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>2.453408836813158e-05</v>
+        <v>2.45340883681316e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>2.447567941120376e-05</v>
+        <v>2.447567941120369e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.448190313571852e-05</v>
+        <v>2.44819031357185e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.447404930310017e-05</v>
+        <v>2.447404930310012e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.448142079524574e-05</v>
+        <v>2.448142079524569e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.451842528242492e-05</v>
+        <v>2.451842528242483e-05</v>
       </c>
     </row>
     <row r="3">
@@ -6850,85 +6850,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.429652687359623e-05</v>
+        <v>2.429652687359618e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>2.429652687359623e-05</v>
+        <v>2.429652687359618e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>2.429652687359623e-05</v>
+        <v>2.429652687359618e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>2.272283118348972e-05</v>
+        <v>2.272283118348974e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>2.429652687359623e-05</v>
+        <v>2.429652687359618e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>2.429652687359623e-05</v>
+        <v>2.429652687359618e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>2.429652687359623e-05</v>
+        <v>2.429652687359618e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>2.429652687359623e-05</v>
+        <v>2.429652687359618e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>2.425665307744272e-05</v>
+        <v>2.425665307744268e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>2.429652687359623e-05</v>
+        <v>2.429652687359618e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>2.429652687359623e-05</v>
+        <v>2.429652687359618e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>2.429652687359623e-05</v>
+        <v>2.429652687359618e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>2.429652687359623e-05</v>
+        <v>2.429652687359618e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>2.429652687359623e-05</v>
+        <v>2.429652687359618e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>2.429652687359623e-05</v>
+        <v>2.429652687359618e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.429652687359623e-05</v>
+        <v>2.429652687359618e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>2.429652687359623e-05</v>
+        <v>2.429652687359618e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>2.429652687359623e-05</v>
+        <v>2.429652687359618e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>2.429652687359623e-05</v>
+        <v>2.429652687359618e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>2.429652687359623e-05</v>
+        <v>2.429652687359618e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>2.485546312994532e-05</v>
+        <v>2.48554631299454e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>2.429652687359623e-05</v>
+        <v>2.429652687359618e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>2.429652687359623e-05</v>
+        <v>2.429652687359618e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.429652687359623e-05</v>
+        <v>2.429652687359618e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.429652687359623e-05</v>
+        <v>2.429652687359618e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.429652687359623e-05</v>
+        <v>2.429652687359618e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.429652687359623e-05</v>
+        <v>2.429652687359618e-05</v>
       </c>
     </row>
     <row r="4">
@@ -6938,85 +6938,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0001949324704881086</v>
+        <v>0.0001949324704881096</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0001914648303080491</v>
+        <v>0.0001914648303080493</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0001988518440526008</v>
+        <v>0.0001988518440526009</v>
       </c>
       <c r="E4" t="n">
-        <v>4.640216669716183e-05</v>
+        <v>4.640216669716195e-05</v>
       </c>
       <c r="F4" t="n">
         <v>0.0001934681720200295</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0002161404592680081</v>
+        <v>0.0002161404592680108</v>
       </c>
       <c r="H4" t="n">
         <v>0.0001938132435258713</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0001901803911196897</v>
+        <v>0.0001901803911196899</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0002017826833575884</v>
+        <v>0.0002017826833575896</v>
       </c>
       <c r="K4" t="n">
         <v>0.0002371029442291189</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0001945664427886836</v>
+        <v>0.0001945664427886855</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0002368680192056151</v>
+        <v>0.0002368680192056158</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0001823015647698952</v>
+        <v>0.0001823015647698956</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0001991040280961771</v>
+        <v>0.0001991040280961775</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0001742838521746036</v>
+        <v>0.000174283852174604</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0001931770790433407</v>
+        <v>0.0001931770790433413</v>
       </c>
       <c r="R4" t="n">
-        <v>0.000196411919793568</v>
+        <v>0.0001964119197935681</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0002046141518496762</v>
+        <v>0.0002046141518496768</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0001963883087828966</v>
+        <v>0.0001963883087828967</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0001920652401674077</v>
+        <v>0.0001920652401674082</v>
       </c>
       <c r="V4" t="n">
         <v>0.0002100862160934048</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0001966172520716651</v>
+        <v>0.000196617252071665</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0001883764631522602</v>
+        <v>0.000188376463152261</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0001940933161402645</v>
+        <v>0.0001940933161402647</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0001880456135659759</v>
+        <v>0.0001880456135659756</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0001862500922297423</v>
+        <v>0.0001862500922297428</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0002115007954970843</v>
+        <v>0.0002115007954970842</v>
       </c>
     </row>
     <row r="5">
@@ -7026,85 +7026,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0002472445308467731</v>
+        <v>0.0002472445308467736</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0004009627458214007</v>
+        <v>0.0004009627458214009</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0004009627458214007</v>
+        <v>0.0004009627458214009</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0003191123307456083</v>
+        <v>0.0003191123307456084</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0002711920322004739</v>
+        <v>0.0002711920322004743</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0004328372190794034</v>
+        <v>0.0004328372190794042</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0004009627458214007</v>
+        <v>0.0004009627458214009</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0004009627458214007</v>
+        <v>0.0004009627458214009</v>
       </c>
       <c r="J5" t="n">
-        <v>0.000400897431307044</v>
+        <v>0.0004008974313070444</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0004009627458214007</v>
+        <v>0.0004009627458214009</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0004009627458214007</v>
+        <v>0.0004009627458214009</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0004009627458213954</v>
+        <v>0.0004009627458213959</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0001823015647698952</v>
+        <v>0.0002818054127261404</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0003145508825010528</v>
+        <v>0.0003145508825010532</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0003065241766161769</v>
+        <v>0.0003065241766161771</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0002170353931500548</v>
+        <v>0.0002170353931500554</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0004009627458214007</v>
+        <v>0.0004009627458214009</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0004009627458214007</v>
+        <v>0.0004009627458214009</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0004009627458214007</v>
+        <v>0.0004009627458214009</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0003259357237580683</v>
+        <v>0.0003259357237580692</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0003586765969376831</v>
+        <v>0.000358676596937683</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0004009929558829972</v>
+        <v>0.0004009929558829982</v>
       </c>
       <c r="X5" t="n">
         <v>0.0002311239730122044</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0005538026144449639</v>
+        <v>0.0005538026144449649</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0002443891360823847</v>
+        <v>0.0002443891360823852</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0004009627458214007</v>
+        <v>0.0004009627458214009</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.000561534275096029</v>
+        <v>0.0005615342750960293</v>
       </c>
     </row>
     <row r="6">
@@ -7114,85 +7114,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0001508634737348493</v>
+        <v>0.0001508634737348495</v>
       </c>
       <c r="C6" t="n">
-        <v>0.000191115201723876</v>
+        <v>0.0001911152017238762</v>
       </c>
       <c r="D6" t="n">
-        <v>0.000191115201723876</v>
+        <v>0.0001911152017238762</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0001818252680533673</v>
+        <v>0.0001818252680533674</v>
       </c>
       <c r="F6" t="n">
-        <v>9.832398133187455e-05</v>
+        <v>9.832398133187469e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0001911152029791372</v>
+        <v>0.0001911152029791374</v>
       </c>
       <c r="H6" t="n">
-        <v>0.000191115201723876</v>
+        <v>0.0001911152017238762</v>
       </c>
       <c r="I6" t="n">
-        <v>0.000191115201723876</v>
+        <v>0.0001911152017238762</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0001910498872095193</v>
+        <v>0.0001910498872095198</v>
       </c>
       <c r="K6" t="n">
-        <v>0.000191115201723876</v>
+        <v>0.0001911152017238762</v>
       </c>
       <c r="L6" t="n">
-        <v>0.000191115201723876</v>
+        <v>0.0001911152017238762</v>
       </c>
       <c r="M6" t="n">
-        <v>0.000191115201723876</v>
+        <v>0.0001911152017238762</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0001823015647698952</v>
+        <v>0.0001911152017238762</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0002044545733455406</v>
+        <v>0.0002044545733455407</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0002073556575351872</v>
+        <v>0.0002073556575351876</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0001911152029791372</v>
+        <v>0.0001911152029791374</v>
       </c>
       <c r="R6" t="n">
-        <v>0.000191115201723876</v>
+        <v>0.0001911152017238762</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0001911152017238759</v>
+        <v>0.0001911152017238762</v>
       </c>
       <c r="T6" t="n">
-        <v>0.000191115201723876</v>
+        <v>0.0001911152017238762</v>
       </c>
       <c r="U6" t="n">
-        <v>0.000191115201723876</v>
+        <v>0.0001911152017238762</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0002372913228770326</v>
+        <v>0.0002372913228770331</v>
       </c>
       <c r="W6" t="n">
-        <v>0.000191115201723876</v>
+        <v>0.0001911152017238762</v>
       </c>
       <c r="X6" t="n">
-        <v>0.000191115201723876</v>
+        <v>0.0001911152017238762</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.000191115201723876</v>
+        <v>0.0001911152017238762</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0001668469895682484</v>
+        <v>0.0001668469895682487</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.000191115201723876</v>
+        <v>0.0001911152017238762</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.000191115201723876</v>
+        <v>0.0001911152017238762</v>
       </c>
     </row>
     <row r="7">
@@ -7202,85 +7202,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.368736232569707e-05</v>
+        <v>2.368736232569702e-05</v>
       </c>
       <c r="C7" t="n">
         <v>2.402396142384212e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.352302152453618e-05</v>
+        <v>2.352302152453609e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.235521368136525e-05</v>
+        <v>2.235521368136529e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.395309989916381e-05</v>
+        <v>2.395309989916378e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.348082718503301e-05</v>
+        <v>2.348082718503289e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.387462345404713e-05</v>
+        <v>2.387462345404711e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.384798527292445e-05</v>
+        <v>2.384798527292435e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.364465666835504e-05</v>
+        <v>2.364465666835498e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>2.366827320255682e-05</v>
+        <v>2.366827320255674e-05</v>
       </c>
       <c r="L7" t="n">
         <v>2.381092413601565e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>2.370149788689164e-05</v>
+        <v>2.370149788689161e-05</v>
       </c>
       <c r="N7" t="n">
         <v>2.383471158212935e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>2.38327638569927e-05</v>
+        <v>2.383276385699257e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>2.384851407883395e-05</v>
+        <v>2.38485140788339e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.379617647685781e-05</v>
+        <v>2.37961764768578e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>2.364137706829623e-05</v>
+        <v>2.364137706829612e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>2.379846004733007e-05</v>
+        <v>2.379846004733004e-05</v>
       </c>
       <c r="T7" t="n">
         <v>2.364756814608269e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>2.370940889114665e-05</v>
+        <v>2.370940889114659e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>2.43439341268615e-05</v>
+        <v>2.434393412686156e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>2.346108160904054e-05</v>
+        <v>2.346108160904049e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>2.381070193449564e-05</v>
+        <v>2.381070193449562e-05</v>
       </c>
       <c r="Y7" t="n">
         <v>2.377034081414402e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.381040056136261e-05</v>
+        <v>2.381040056136249e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.377259643845197e-05</v>
+        <v>2.3772596438452e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.356114662454244e-05</v>
+        <v>2.356114662454238e-05</v>
       </c>
     </row>
     <row r="8">
@@ -7290,85 +7290,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.421741868265813e-05</v>
+        <v>2.421741868265799e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.431527934217638e-05</v>
+        <v>2.431527934217635e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.417297108488712e-05</v>
+        <v>2.41729710848871e-05</v>
       </c>
       <c r="E8" t="n">
         <v>2.263318510648235e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.429574094068018e-05</v>
+        <v>2.42957409406802e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.415826427563921e-05</v>
+        <v>2.415826427563914e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.427372593698089e-05</v>
+        <v>2.427372593698082e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.42655777732703e-05</v>
+        <v>2.426557777327025e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.417508925946108e-05</v>
+        <v>2.417508925946096e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.421405312813424e-05</v>
+        <v>2.421405312813419e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>2.425365522351572e-05</v>
+        <v>2.425365522351576e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>2.422426100502179e-05</v>
+        <v>2.422426100502176e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>2.426106618585769e-05</v>
+        <v>2.426106618585767e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>2.425900253388948e-05</v>
+        <v>2.425900253388947e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>2.426342234592365e-05</v>
+        <v>2.426342234592363e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.425029356132937e-05</v>
+        <v>2.42502935613294e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>2.420723350337084e-05</v>
+        <v>2.420723350337085e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>2.42496857740786e-05</v>
+        <v>2.424968577407857e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>2.420847679584368e-05</v>
+        <v>2.420847679584362e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>2.422449601021339e-05</v>
+        <v>2.422449601021332e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>2.479364704659874e-05</v>
+        <v>2.479364704659868e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>2.415395811035267e-05</v>
+        <v>2.415395811035255e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>2.425462751568077e-05</v>
+        <v>2.425462751568073e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.424248680181225e-05</v>
+        <v>2.424248680181229e-05</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.425286028184122e-05</v>
+        <v>2.425286028184125e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.424303077758787e-05</v>
+        <v>2.424303077758778e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.418382492558764e-05</v>
+        <v>2.418382492558757e-05</v>
       </c>
     </row>
   </sheetData>
@@ -7534,85 +7534,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.473386832549165e-05</v>
+        <v>2.473386832549166e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>2.465196255622638e-05</v>
+        <v>2.465196255622641e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>2.481388809085767e-05</v>
+        <v>2.481388809085769e-05</v>
       </c>
       <c r="E2" t="n">
         <v>2.295372970180494e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>2.467183164413152e-05</v>
+        <v>2.467183164413154e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>2.469916342307253e-05</v>
+        <v>2.469916342307254e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>2.468260546655806e-05</v>
+        <v>2.468260546655808e-05</v>
       </c>
       <c r="I2" t="n">
         <v>2.479379219726702e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>2.46718516352557e-05</v>
+        <v>2.467185163525574e-05</v>
       </c>
       <c r="K2" t="n">
         <v>2.473743906671073e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>2.472592746505035e-05</v>
+        <v>2.472592746505033e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>2.477561056990974e-05</v>
+        <v>2.477561056990973e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>2.468903457628237e-05</v>
+        <v>2.468903457628238e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>2.466124114154222e-05</v>
+        <v>2.466124114154223e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>2.465901897105443e-05</v>
+        <v>2.465901897105444e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.470143557162209e-05</v>
+        <v>2.470143557162208e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>2.47437829281706e-05</v>
+        <v>2.474378292817061e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>2.470923051304203e-05</v>
+        <v>2.470923051304206e-05</v>
       </c>
       <c r="T2" t="n">
         <v>2.47411198905075e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>2.470597549803552e-05</v>
+        <v>2.47059754980355e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>2.528847813023615e-05</v>
+        <v>2.528847813023612e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>2.475649559023274e-05</v>
+        <v>2.475649559023275e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>2.467917284968477e-05</v>
+        <v>2.467917284968478e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.466567078570055e-05</v>
+        <v>2.466567078570057e-05</v>
       </c>
       <c r="Z2" t="n">
         <v>2.470985105806146e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.474950736009211e-05</v>
+        <v>2.474950736009212e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.473130034871718e-05</v>
+        <v>2.473130034871717e-05</v>
       </c>
     </row>
     <row r="3">
@@ -7622,85 +7622,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.44699190114723e-05</v>
+        <v>2.446991901147228e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>2.44699190114723e-05</v>
+        <v>2.446991901147228e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>2.44699190114723e-05</v>
+        <v>2.446991901147228e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>2.282090434886415e-05</v>
+        <v>2.282090434886414e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>2.44699190114723e-05</v>
+        <v>2.446991901147228e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>2.44699190114723e-05</v>
+        <v>2.446991901147228e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>2.44699190114723e-05</v>
+        <v>2.446991901147228e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>2.44699190114723e-05</v>
+        <v>2.446991901147228e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>2.443131564346396e-05</v>
+        <v>2.443131564346395e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>2.44699190114723e-05</v>
+        <v>2.446991901147228e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>2.44699190114723e-05</v>
+        <v>2.446991901147228e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>2.44699190114723e-05</v>
+        <v>2.446991901147228e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>2.44699190114723e-05</v>
+        <v>2.446991901147228e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>2.44699190114723e-05</v>
+        <v>2.446991901147228e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>2.44699190114723e-05</v>
+        <v>2.446991901147228e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.44699190114723e-05</v>
+        <v>2.446991901147228e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>2.44699190114723e-05</v>
+        <v>2.446991901147228e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>2.44699190114723e-05</v>
+        <v>2.446991901147228e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>2.44699190114723e-05</v>
+        <v>2.446991901147228e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>2.44699190114723e-05</v>
+        <v>2.446991901147228e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>2.505854393544179e-05</v>
+        <v>2.505854393544182e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>2.44699190114723e-05</v>
+        <v>2.446991901147228e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>2.44699190114723e-05</v>
+        <v>2.446991901147228e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.44699190114723e-05</v>
+        <v>2.446991901147228e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.44699190114723e-05</v>
+        <v>2.446991901147228e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.44699190114723e-05</v>
+        <v>2.446991901147228e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.44699190114723e-05</v>
+        <v>2.446991901147228e-05</v>
       </c>
     </row>
     <row r="4">
@@ -7710,85 +7710,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0001940384919068758</v>
+        <v>0.000194038491906876</v>
       </c>
       <c r="C4" t="n">
         <v>0.0002030184276311245</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0002304410502426472</v>
+        <v>0.0002304410502426474</v>
       </c>
       <c r="E4" t="n">
-        <v>5.759405454378963e-05</v>
+        <v>5.759405454378976e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0001984559958774113</v>
+        <v>0.0001984559958774114</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0002169722950850625</v>
+        <v>0.0002169722950850624</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0001901460351954898</v>
+        <v>0.0001901460351954899</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0002170070569325486</v>
+        <v>0.0002170070569325489</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0002095009795461507</v>
+        <v>0.0002095009795461508</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0002464177104655579</v>
+        <v>0.0002464177104655582</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0002236292738848573</v>
+        <v>0.0002236292738848572</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0002547565643436739</v>
+        <v>0.0002547565643436741</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0001818234508085228</v>
+        <v>0.0001818234508085232</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0001935546456398531</v>
+        <v>0.0001935546456398591</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0001768378949617927</v>
+        <v>0.0001768378949617929</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0002084919445423826</v>
+        <v>0.0002084919445423828</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0002037654590549652</v>
+        <v>0.0002037654590549655</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0002064696312696723</v>
+        <v>0.0002064696312696722</v>
       </c>
       <c r="T4" t="n">
-        <v>0.000205971121921134</v>
+        <v>0.0002059711219211339</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0002114707552410077</v>
+        <v>0.0002114707552410074</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0002154178205080431</v>
+        <v>0.000215417820508043</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0001963919067563909</v>
+        <v>0.0001963919067563912</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0001931565875656923</v>
+        <v>0.0001931565875656924</v>
       </c>
       <c r="Y4" t="n">
         <v>0.0001831987303872266</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0002026669878591232</v>
+        <v>0.0002026669878591235</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0001971881773624919</v>
+        <v>0.0001971881773624921</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0002138197284857193</v>
+        <v>0.0002138197284857197</v>
       </c>
     </row>
     <row r="5">
@@ -7798,85 +7798,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0002313402410822832</v>
+        <v>0.0002313402410822836</v>
       </c>
       <c r="C5" t="n">
-        <v>0.000374799678591451</v>
+        <v>0.0003747996785914516</v>
       </c>
       <c r="D5" t="n">
-        <v>0.000374799678591451</v>
+        <v>0.0003747996785914516</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0002984117599014208</v>
+        <v>0.000298411759901421</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0002536895448034012</v>
+        <v>0.0002536895448034018</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0004045469275121204</v>
+        <v>0.000404546927512121</v>
       </c>
       <c r="H5" t="n">
-        <v>0.000374799678591451</v>
+        <v>0.0003747996785914516</v>
       </c>
       <c r="I5" t="n">
-        <v>0.000374799678591451</v>
+        <v>0.0003747996785914516</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0003747346576087821</v>
+        <v>0.0003747346576087829</v>
       </c>
       <c r="K5" t="n">
-        <v>0.000374799678591451</v>
+        <v>0.0003747996785914516</v>
       </c>
       <c r="L5" t="n">
-        <v>0.000374799678591451</v>
+        <v>0.0003747996785914517</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0003747996785914472</v>
+        <v>0.000374799678591448</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0001818234508085228</v>
+        <v>0.0002635946142873688</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0002941547315488915</v>
+        <v>0.0002941547315488922</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0002866637083706911</v>
+        <v>0.0002866637083706917</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0002031471873032059</v>
+        <v>0.0002031471873032062</v>
       </c>
       <c r="R5" t="n">
-        <v>0.000374799678591451</v>
+        <v>0.0003747996785914516</v>
       </c>
       <c r="S5" t="n">
-        <v>0.000374799678591451</v>
+        <v>0.0003747996785914516</v>
       </c>
       <c r="T5" t="n">
-        <v>0.000374799678591451</v>
+        <v>0.0003747996785914516</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0003047827736548145</v>
+        <v>0.000304782773654815</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0003353226173584022</v>
+        <v>0.0003353226173584029</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0003748278725070342</v>
+        <v>0.0003748278725070348</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0002162955298247674</v>
+        <v>0.0002162955298247677</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0005174445159293981</v>
+        <v>0.0005174445159293991</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0002286754083762927</v>
+        <v>0.0002286754083762929</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.000374799678591451</v>
+        <v>0.0003747996785914516</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0005246550569763942</v>
+        <v>0.0005246550569763955</v>
       </c>
     </row>
     <row r="6">
@@ -7886,7 +7886,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0001339027644470828</v>
+        <v>0.0001339027644470829</v>
       </c>
       <c r="C6" t="n">
         <v>0.0001693971649057563</v>
@@ -7898,10 +7898,10 @@
         <v>0.0001612052029958015</v>
       </c>
       <c r="F6" t="n">
-        <v>8.757288291773104e-05</v>
+        <v>8.757288291773111e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0001693971661237503</v>
+        <v>0.0001693971661237504</v>
       </c>
       <c r="H6" t="n">
         <v>0.0001693971649057563</v>
@@ -7910,7 +7910,7 @@
         <v>0.0001693971649057563</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0001693321439230876</v>
+        <v>0.0001693321439230877</v>
       </c>
       <c r="K6" t="n">
         <v>0.0001693971649057563</v>
@@ -7922,16 +7922,16 @@
         <v>0.0001693971649057563</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0001818234508085228</v>
+        <v>0.0001693971649057563</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0001811599643634343</v>
+        <v>0.0001811599643634345</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0001837181711649413</v>
+        <v>0.0001837181711649414</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0001693971661237503</v>
+        <v>0.0001693971661237504</v>
       </c>
       <c r="R6" t="n">
         <v>0.0001693971649057563</v>
@@ -7946,7 +7946,7 @@
         <v>0.0001693971649057563</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0002100853923393916</v>
+        <v>0.0002100853923393917</v>
       </c>
       <c r="W6" t="n">
         <v>0.0001693971649057563</v>
@@ -7958,7 +7958,7 @@
         <v>0.0001693971649057563</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0001479971981980639</v>
+        <v>0.000147997198198064</v>
       </c>
       <c r="AA6" t="n">
         <v>0.0001693971649057563</v>
@@ -7974,85 +7974,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.346038598815985e-05</v>
+        <v>2.346038598815989e-05</v>
       </c>
       <c r="C7" t="n">
         <v>2.395876223768783e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.301114254590061e-05</v>
+        <v>2.301114254590063e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.212545314156109e-05</v>
+        <v>2.212545314156108e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.384757447289223e-05</v>
+        <v>2.384757447289222e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.366745768220611e-05</v>
+        <v>2.366745768220612e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.378659880771299e-05</v>
+        <v>2.378659880771298e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.313184169950339e-05</v>
+        <v>2.313184169950338e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.355646912844652e-05</v>
+        <v>2.355646912844655e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>2.345716758197098e-05</v>
+        <v>2.345716758197097e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>2.351526088253459e-05</v>
+        <v>2.351526088253458e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>2.324100362492907e-05</v>
+        <v>2.324100362492905e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>2.373833407034759e-05</v>
+        <v>2.373833407034761e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>2.389153764437877e-05</v>
+        <v>2.38915376443788e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>2.390405995102593e-05</v>
+        <v>2.390405995102595e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.366712760057777e-05</v>
+        <v>2.366712760057779e-05</v>
       </c>
       <c r="R7" t="n">
         <v>2.342692836724276e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>2.361041084157888e-05</v>
+        <v>2.361041084157889e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>2.343820913752555e-05</v>
+        <v>2.343820913752557e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>2.363213022781005e-05</v>
+        <v>2.363213022781007e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>2.418577373277161e-05</v>
+        <v>2.418577373277165e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>2.33368521437454e-05</v>
+        <v>2.333685214374541e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>2.379932462342744e-05</v>
+        <v>2.379932462342742e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.387427361054642e-05</v>
+        <v>2.387427361054641e-05</v>
       </c>
       <c r="Z7" t="n">
         <v>2.360452469503649e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.337922968145536e-05</v>
+        <v>2.337922968145537e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.349504854532506e-05</v>
+        <v>2.349504854532508e-05</v>
       </c>
     </row>
     <row r="8">
@@ -8062,52 +8062,52 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.42745275826936e-05</v>
+        <v>2.427452758269361e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.441938459519449e-05</v>
+        <v>2.44193845951945e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.415014015017779e-05</v>
+        <v>2.415014015017781e-05</v>
       </c>
       <c r="E8" t="n">
         <v>2.263729718621055e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.438866289578323e-05</v>
+        <v>2.438866289578325e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.433404096096388e-05</v>
+        <v>2.433404096096391e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.437169259623533e-05</v>
+        <v>2.43716925962353e-05</v>
       </c>
       <c r="I8" t="n">
         <v>2.418496275612178e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.427379368295238e-05</v>
+        <v>2.427379368295239e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.427663393884033e-05</v>
+        <v>2.427663393884036e-05</v>
       </c>
       <c r="L8" t="n">
         <v>2.429155497406871e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>2.42164501527116e-05</v>
+        <v>2.421645015271162e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>2.435616109664774e-05</v>
+        <v>2.435616109664779e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>2.439807577632262e-05</v>
+        <v>2.439807577632264e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>2.44015512952655e-05</v>
+        <v>2.440155129526553e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.433616292132062e-05</v>
+        <v>2.433616292132065e-05</v>
       </c>
       <c r="R8" t="n">
         <v>2.426921886123219e-05</v>
@@ -8116,31 +8116,31 @@
         <v>2.431815155665054e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>2.427168860999744e-05</v>
+        <v>2.427168860999743e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>2.432477893159476e-05</v>
+        <v>2.432477893159474e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>2.489136490666761e-05</v>
+        <v>2.489136490666759e-05</v>
       </c>
       <c r="W8" t="n">
         <v>2.424094655454715e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>2.437405026606684e-05</v>
+        <v>2.437405026606685e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.439465023007005e-05</v>
+        <v>2.439465023007002e-05</v>
       </c>
       <c r="Z8" t="n">
         <v>2.431609388623513e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.425324023911376e-05</v>
+        <v>2.425324023911377e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.428773117989236e-05</v>
+        <v>2.428773117989235e-05</v>
       </c>
     </row>
   </sheetData>
